--- a/Thesis_TSSP_NEW_M1_Results_10_Scenarios.xlsx
+++ b/Thesis_TSSP_NEW_M1_Results_10_Scenarios.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4/5/2026 15:52</t>
+          <t>4/5/2026 15:48</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -478,7 +478,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4/5/2026 13:03</t>
+          <t>4/5/2026 15:48</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -488,7 +488,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4/5/2026 16:08</t>
+          <t>4/5/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -500,22 +500,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4/5/2026 10:44</t>
+          <t>4/5/2026 15:48</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4/5/2026 16:08</t>
+          <t>4/5/2026 15:48</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -525,7 +525,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4/5/2026 16:08</t>
+          <t>4/5/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -537,32 +537,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4/5/2026 16:08</t>
+          <t>4/5/2026 15:48</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4/5/2026 11:56</t>
+          <t>4/5/2026 15:48</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -574,12 +574,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4/5/2026 16:08</t>
+          <t>4/5/2026 09:09</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -589,17 +589,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4/5/2026 08:53</t>
+          <t>4/5/2026 15:48</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4/5/2026 16:08</t>
+          <t>4/5/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -616,27 +616,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4/5/2026 15:33</t>
+          <t>4/5/2026 15:48</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4/5/2026 15:36</t>
+          <t>4/5/2026 09:08</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4/5/2026 16:08</t>
+          <t>4/5/2026 12:42</t>
         </is>
       </c>
     </row>
@@ -648,12 +648,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4/5/2026 14:27</t>
+          <t>4/5/2026 07:19</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -663,17 +663,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4/5/2026 09:27</t>
+          <t>4/5/2026 07:20</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4/5/2026 08:09</t>
+          <t>4/5/2026 07:20</t>
         </is>
       </c>
     </row>
@@ -685,12 +685,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4/5/2026 14:55</t>
+          <t>4/5/2026 06:48</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4/5/2026 16:06</t>
+          <t>4/5/2026 07:03</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4/5/2026 12:10</t>
+          <t>4/5/2026 06:48</t>
         </is>
       </c>
     </row>
@@ -722,32 +722,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>4/5/2026 09:23</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Transport Cart 2</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>4/5/2026 09:25</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Transport Cart 2</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>4/5/2026 16:07</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4/5/2026 15:34</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -774,17 +774,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4/5/2026 11:14</t>
+          <t>4/5/2026 08:27</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4/5/2026 15:57</t>
+          <t>4/5/2026 10:16</t>
         </is>
       </c>
     </row>
@@ -796,7 +796,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -806,12 +806,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4/5/2026 09:32</t>
+          <t>4/5/2026 07:38</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -821,7 +821,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4/5/2026 11:03</t>
+          <t>4/5/2026 07:27</t>
         </is>
       </c>
     </row>
@@ -833,32 +833,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4/5/2026 14:51</t>
+          <t>4/5/2026 10:46</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 09:29</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4/5/2026 15:34</t>
+          <t>4/5/2026 08:09</t>
         </is>
       </c>
     </row>
@@ -870,32 +870,32 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4/5/2026 09:46</t>
+          <t>4/5/2026 08:25</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4/5/2026 08:26</t>
+          <t>4/5/2026 08:24</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4/5/2026 15:05</t>
+          <t>4/5/2026 12:17</t>
         </is>
       </c>
     </row>
@@ -907,32 +907,32 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4/5/2026 09:53</t>
+          <t>4/5/2026 13:02</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4/5/2026 08:56</t>
+          <t>4/5/2026 08:40</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4/5/2026 16:06</t>
+          <t>4/5/2026 13:42</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4/5/2026 09:35</t>
+          <t>4/5/2026 15:47</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -959,17 +959,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4/5/2026 14:47</t>
+          <t>4/5/2026 06:18</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4/5/2026 07:41</t>
+          <t>4/5/2026 08:12</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4/5/2026 13:25</t>
+          <t>4/5/2026 07:08</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -996,17 +996,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4/5/2026 15:34</t>
+          <t>4/5/2026 07:14</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4/5/2026 13:47</t>
+          <t>4/5/2026 12:19</t>
         </is>
       </c>
     </row>
@@ -1018,32 +1018,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 10:44</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4/5/2026 14:37</t>
+          <t>4/5/2026 09:11</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:33</t>
+          <t>4/5/2026 12:00</t>
         </is>
       </c>
     </row>
@@ -1055,32 +1055,32 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4/5/2026 11:59</t>
+          <t>4/5/2026 15:45</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4/5/2026 13:32</t>
+          <t>4/5/2026 15:21</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4/5/2026 10:56</t>
+          <t>4/5/2026 12:53</t>
         </is>
       </c>
     </row>
@@ -1092,22 +1092,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4/5/2026 09:24</t>
+          <t>4/5/2026 15:35</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4/5/2026 15:22</t>
+          <t>4/5/2026 13:03</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4/5/2026 09:18</t>
+          <t>4/5/2026 10:58</t>
         </is>
       </c>
     </row>
@@ -1129,32 +1129,32 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4/5/2026 10:52</t>
+          <t>4/5/2026 08:25</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4/5/2026 15:16</t>
+          <t>4/5/2026 11:17</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4/5/2026 08:22</t>
+          <t>4/5/2026 09:02</t>
         </is>
       </c>
     </row>
@@ -1171,27 +1171,27 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4/5/2026 09:24</t>
+          <t>4/5/2026 13:45</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4/5/2026 16:05</t>
+          <t>4/5/2026 14:33</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4/5/2026 08:32</t>
+          <t>4/5/2026 15:48</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4/5/2026 12:17</t>
+          <t>4/5/2026 13:32</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1218,17 +1218,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4/5/2026 16:08</t>
+          <t>4/5/2026 10:39</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>4/5/2026 15:53</t>
+          <t>4/5/2026 15:46</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>442.60 min</t>
+          <t>435.90 min</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>33.00 min</t>
+          <t>31.98 min</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>93.60 min</t>
+          <t>88.60 min</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>148.00 min</t>
+          <t>99.00 min</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>30.40 min</t>
+          <t>16.30 min</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11.50/8.70/14.60 min</t>
+          <t>4.00/5.40/9.80 min</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1103523 / 65646</t>
+          <t>1057323 / 63646</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>44.2760 sec</t>
+          <t>38.3130 sec</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0.9581 %</t>
+          <t>0.5614 %</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>29.86 min | 84.00 min</t>
+          <t>30.67 min | 96.00 min</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>32.43 min | 86.00 min</t>
+          <t>32.43 min | 95.00 min</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>31.43 min | 88.00 min</t>
+          <t>33.52 min | 99.00 min</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>29.95 min | 80.00 min</t>
+          <t>29.90 min | 80.00 min</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>36.38 min | 83.00 min</t>
+          <t>32.81 min | 78.00 min</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>36.95 min | 90.00 min</t>
+          <t>32.14 min | 84.00 min</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>35.71 min | 94.00 min</t>
+          <t>34.29 min | 85.00 min</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>33.95 min | 148.00 min</t>
+          <t>33.19 min | 97.00 min</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>31.67 min | 92.00 min</t>
+          <t>30.57 min | 92.00 min</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>31.62 min | 91.00 min</t>
+          <t>30.24 min | 80.00 min</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>9.16</v>
+        <v>11.63</v>
       </c>
     </row>
     <row r="41">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>16.03</v>
+        <v>11.63</v>
       </c>
     </row>
     <row r="42">
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>9.16</v>
+        <v>18.61</v>
       </c>
     </row>
     <row r="43">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>13.74</v>
+        <v>6.98</v>
       </c>
     </row>
     <row r="44">
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2.69</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="45">
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3.59</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="46">
@@ -1697,7 +1697,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3.14</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="47">
@@ -1707,7 +1707,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>24.79</v>
+        <v>29.36</v>
       </c>
     </row>
     <row r="48">
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>28.92</v>
+        <v>25.17</v>
       </c>
     </row>
     <row r="49">
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>33.05</v>
+        <v>33.56</v>
       </c>
     </row>
   </sheetData>
@@ -1918,22 +1918,22 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4/5/2026 12:12</t>
+          <t>4/5/2026 12:24</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4/5/2026 12:58</t>
+          <t>4/5/2026 13:10</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M3" t="n">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
@@ -2518,22 +2518,22 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:28</t>
+          <t>4/5/2026 11:33</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:48</t>
+          <t>4/5/2026 11:53</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M13" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -3092,48 +3092,48 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4/5/2026 11:38</t>
+          <t>4/5/2026 11:43</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4/5/2026 11:48</t>
+          <t>4/5/2026 11:53</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>4/5/2026 11:48</t>
+          <t>4/5/2026 11:54</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4/5/2026 11:50</t>
+          <t>4/5/2026 11:56</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>4/5/2026 11:50</t>
+          <t>4/5/2026 11:56</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>4/5/2026 12:13</t>
+          <t>4/5/2026 12:19</t>
         </is>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -3178,22 +3178,22 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>4/5/2026 12:14</t>
+          <t>4/5/2026 12:23</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>4/5/2026 13:00</t>
+          <t>4/5/2026 13:09</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M24" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
@@ -3585,35 +3585,35 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>4/5/2026 12:47</t>
+          <t>4/5/2026 12:56</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4/5/2026 12:49</t>
+          <t>4/5/2026 12:58</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>4/5/2026 13:07</t>
+          <t>4/5/2026 13:13</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>4/5/2026 13:36</t>
+          <t>4/5/2026 13:42</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="M31" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="N31" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32">
@@ -3718,22 +3718,22 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>4/5/2026 11:58</t>
+          <t>4/5/2026 11:50</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>4/5/2026 12:04</t>
+          <t>4/5/2026 11:56</t>
         </is>
       </c>
       <c r="L33" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="N33" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -3752,25 +3752,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>4/5/2026 08:32</t>
+          <t>4/5/2026 08:24</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>4/5/2026 08:45</t>
+          <t>4/5/2026 08:37</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>4/5/2026 08:45</t>
+          <t>4/5/2026 08:37</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>4/5/2026 08:46</t>
+          <t>4/5/2026 08:38</t>
         </is>
       </c>
       <c r="I34" t="n">
@@ -3778,22 +3778,22 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>4/5/2026 08:46</t>
+          <t>4/5/2026 08:38</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:05</t>
         </is>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="N34" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -4232,48 +4232,48 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4/5/2026 11:29</t>
+          <t>4/5/2026 11:28</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>4/5/2026 11:38</t>
+          <t>4/5/2026 11:37</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>4/5/2026 11:56</t>
+          <t>4/5/2026 11:45</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>4/5/2026 11:59</t>
+          <t>4/5/2026 11:48</t>
         </is>
       </c>
       <c r="I42" t="n">
+        <v>8</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>4/5/2026 11:58</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>4/5/2026 12:23</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>10</v>
+      </c>
+      <c r="M42" t="n">
+        <v>55</v>
+      </c>
+      <c r="N42" t="n">
         <v>18</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>4/5/2026 12:04</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>4/5/2026 12:29</t>
-        </is>
-      </c>
-      <c r="L42" t="n">
-        <v>5</v>
-      </c>
-      <c r="M42" t="n">
-        <v>61</v>
-      </c>
-      <c r="N42" t="n">
-        <v>24</v>
       </c>
     </row>
     <row r="43">
@@ -4292,25 +4292,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4/5/2026 08:56</t>
+          <t>4/5/2026 08:57</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>4/5/2026 09:02</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>4/5/2026 09:02</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>4/5/2026 09:04</t>
+          <t>4/5/2026 09:05</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -4318,22 +4318,22 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>4/5/2026 09:04</t>
+          <t>4/5/2026 09:05</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>4/5/2026 09:07</t>
+          <t>4/5/2026 09:08</t>
         </is>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -4498,22 +4498,22 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>4/5/2026 13:02</t>
+          <t>4/5/2026 13:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>4/5/2026 13:09</t>
+          <t>4/5/2026 13:07</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="N46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -4952,48 +4952,48 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>4/5/2026 08:05</t>
+          <t>4/5/2026 08:10</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>4/5/2026 08:12</t>
+          <t>4/5/2026 08:17</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>4/5/2026 08:12</t>
+          <t>4/5/2026 08:24</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>4/5/2026 08:14</t>
+          <t>4/5/2026 08:26</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>4/5/2026 08:14</t>
+          <t>4/5/2026 08:26</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>4/5/2026 08:34</t>
+          <t>4/5/2026 08:46</t>
         </is>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="55">
@@ -5432,48 +5432,48 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>4/5/2026 08:20</t>
+          <t>4/5/2026 08:30</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>4/5/2026 08:33</t>
+          <t>4/5/2026 08:43</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>4/5/2026 08:33</t>
+          <t>4/5/2026 08:52</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>4/5/2026 08:36</t>
+          <t>4/5/2026 08:55</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>4/5/2026 08:36</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>4/5/2026 09:25</t>
+          <t>4/5/2026 09:59</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M62" t="n">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="N62" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="63">
@@ -5505,16 +5505,16 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>4/5/2026 10:12</t>
+          <t>4/5/2026 10:13</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>4/5/2026 10:14</t>
+          <t>4/5/2026 10:15</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M63" t="n">
         <v>38</v>
@@ -6118,22 +6118,22 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>4/5/2026 12:54</t>
+          <t>4/5/2026 12:47</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>4/5/2026 13:23</t>
+          <t>4/5/2026 13:16</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M73" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="N73" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -6718,22 +6718,22 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>4/5/2026 08:57</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>4/5/2026 09:23</t>
+          <t>4/5/2026 09:29</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M83" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="84">
@@ -7005,35 +7005,35 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>4/5/2026 13:15</t>
+          <t>4/5/2026 13:00</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>4/5/2026 13:17</t>
+          <t>4/5/2026 13:02</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>4/5/2026 13:24</t>
+          <t>4/5/2026 13:02</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>4/5/2026 13:31</t>
+          <t>4/5/2026 13:09</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M88" t="n">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="N88" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -7078,22 +7078,22 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>4/5/2026 12:57</t>
+          <t>4/5/2026 13:09</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>4/5/2026 13:24</t>
+          <t>4/5/2026 13:36</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M89" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="N89" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="90">
@@ -7318,22 +7318,22 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>4/5/2026 09:30</t>
+          <t>4/5/2026 09:34</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>4/5/2026 10:11</t>
+          <t>4/5/2026 10:15</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M93" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="N93" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94">
@@ -7532,48 +7532,48 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
+          <t>4/5/2026 12:23</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
           <t>4/5/2026 12:36</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>4/5/2026 12:49</t>
-        </is>
-      </c>
       <c r="F97" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>4/5/2026 12:53</t>
+          <t>4/5/2026 12:36</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>4/5/2026 12:55</t>
+          <t>4/5/2026 12:38</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>4/5/2026 13:15</t>
+          <t>4/5/2026 12:38</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>4/5/2026 13:46</t>
+          <t>4/5/2026 13:09</t>
         </is>
       </c>
       <c r="L97" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>83</v>
+        <v>46</v>
       </c>
       <c r="N97" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -7772,48 +7772,48 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>4/5/2026 09:29</t>
+          <t>4/5/2026 09:09</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>4/5/2026 09:43</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>4/5/2026 09:49</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>4/5/2026 09:51</t>
+          <t>4/5/2026 09:25</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>4/5/2026 10:11</t>
+          <t>4/5/2026 09:25</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>4/5/2026 10:20</t>
+          <t>4/5/2026 09:34</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M101" t="n">
-        <v>71</v>
+        <v>25</v>
       </c>
       <c r="N101" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -7978,22 +7978,22 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>4/5/2026 09:00</t>
+          <t>4/5/2026 09:09</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>4/5/2026 09:26</t>
+          <t>4/5/2026 09:35</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M104" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="N104" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="105">
@@ -8025,35 +8025,35 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>4/5/2026 12:43</t>
+          <t>4/5/2026 12:50</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>4/5/2026 12:45</t>
+          <t>4/5/2026 12:52</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>4/5/2026 12:45</t>
+          <t>4/5/2026 12:52</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>4/5/2026 13:15</t>
+          <t>4/5/2026 13:22</t>
         </is>
       </c>
       <c r="L105" t="n">
         <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="N105" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="106">
@@ -8098,22 +8098,22 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:07</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="L106" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M106" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="N106" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107">
@@ -8625,35 +8625,35 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>4/5/2026 08:57</t>
+          <t>4/5/2026 08:37</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>4/5/2026 09:00</t>
+          <t>4/5/2026 08:40</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 08:40</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>4/5/2026 09:50</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="N115" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -8672,48 +8672,48 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>4/5/2026 11:13</t>
+          <t>4/5/2026 11:04</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>4/5/2026 11:17</t>
+          <t>4/5/2026 11:08</t>
         </is>
       </c>
       <c r="F116" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>4/5/2026 11:34</t>
+          <t>4/5/2026 11:08</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>4/5/2026 11:36</t>
+          <t>4/5/2026 11:10</t>
         </is>
       </c>
       <c r="I116" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>4/5/2026 11:56</t>
+          <t>4/5/2026 11:10</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>4/5/2026 12:17</t>
+          <t>4/5/2026 11:31</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M116" t="n">
-        <v>73</v>
+        <v>27</v>
       </c>
       <c r="N116" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -9058,22 +9058,22 @@
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>4/5/2026 09:29</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M122" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="N122" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="123">
@@ -9152,48 +9152,48 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>4/5/2026 12:26</t>
+          <t>4/5/2026 12:41</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>4/5/2026 12:43</t>
+          <t>4/5/2026 12:58</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>4/5/2026 12:43</t>
+          <t>4/5/2026 13:06</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>4/5/2026 12:45</t>
+          <t>4/5/2026 13:08</t>
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>4/5/2026 12:45</t>
+          <t>4/5/2026 13:08</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>4/5/2026 13:14</t>
+          <t>4/5/2026 13:37</t>
         </is>
       </c>
       <c r="L124" t="n">
         <v>0</v>
       </c>
       <c r="M124" t="n">
-        <v>48</v>
+        <v>71</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="125">
@@ -9285,35 +9285,35 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>4/5/2026 09:07</t>
+          <t>4/5/2026 08:47</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 08:49</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>4/5/2026 09:29</t>
+          <t>4/5/2026 08:49</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>4/5/2026 10:02</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M126" t="n">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="N126" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -9885,35 +9885,35 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>4/5/2026 13:01</t>
+          <t>4/5/2026 12:55</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>4/5/2026 13:03</t>
+          <t>4/5/2026 12:57</t>
         </is>
       </c>
       <c r="I136" t="n">
+        <v>9</v>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>4/5/2026 13:12</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>4/5/2026 13:41</t>
+        </is>
+      </c>
+      <c r="L136" t="n">
         <v>15</v>
       </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>4/5/2026 13:06</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>4/5/2026 13:35</t>
-        </is>
-      </c>
-      <c r="L136" t="n">
-        <v>3</v>
-      </c>
       <c r="M136" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="N136" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="137">
@@ -10018,22 +10018,22 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>4/5/2026 11:54</t>
+          <t>4/5/2026 11:52</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>4/5/2026 12:00</t>
+          <t>4/5/2026 11:58</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M138" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="N138" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
@@ -10052,48 +10052,48 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>4/5/2026 12:43</t>
+          <t>4/5/2026 12:23</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>4/5/2026 13:00</t>
+          <t>4/5/2026 12:40</t>
         </is>
       </c>
       <c r="F139" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>4/5/2026 13:13</t>
+          <t>4/5/2026 12:40</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>4/5/2026 13:14</t>
+          <t>4/5/2026 12:41</t>
         </is>
       </c>
       <c r="I139" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>4/5/2026 13:14</t>
+          <t>4/5/2026 12:41</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>4/5/2026 13:45</t>
+          <t>4/5/2026 13:12</t>
         </is>
       </c>
       <c r="L139" t="n">
         <v>0</v>
       </c>
       <c r="M139" t="n">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="N139" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
@@ -10112,48 +10112,48 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>4/5/2026 11:23</t>
+          <t>4/5/2026 11:03</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>4/5/2026 11:34</t>
+          <t>4/5/2026 11:14</t>
         </is>
       </c>
       <c r="F140" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>4/5/2026 11:37</t>
+          <t>4/5/2026 11:14</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>4/5/2026 11:40</t>
+          <t>4/5/2026 11:17</t>
         </is>
       </c>
       <c r="I140" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>4/5/2026 12:00</t>
+          <t>4/5/2026 11:17</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>4/5/2026 12:37</t>
+          <t>4/5/2026 11:54</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M140" t="n">
-        <v>94</v>
+        <v>51</v>
       </c>
       <c r="N140" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -10412,48 +10412,48 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>4/5/2026 12:26</t>
+          <t>4/5/2026 12:31</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>4/5/2026 12:43</t>
+          <t>4/5/2026 12:48</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>4/5/2026 12:43</t>
+          <t>4/5/2026 12:58</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>4/5/2026 12:45</t>
+          <t>4/5/2026 13:00</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>4/5/2026 12:45</t>
+          <t>4/5/2026 13:12</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>4/5/2026 13:14</t>
+          <t>4/5/2026 13:41</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M145" t="n">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="N145" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="146">
@@ -10558,22 +10558,22 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>4/5/2026 12:44</t>
+          <t>4/5/2026 12:59</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>4/5/2026 13:14</t>
+          <t>4/5/2026 13:29</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="M147" t="n">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="N147" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
     </row>
     <row r="148">
@@ -10712,48 +10712,48 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>4/5/2026 11:54</t>
+          <t>4/5/2026 11:34</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>4/5/2026 12:35</t>
+          <t>4/5/2026 12:15</t>
         </is>
       </c>
       <c r="F150" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>4/5/2026 12:54</t>
+          <t>4/5/2026 12:15</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>4/5/2026 12:56</t>
+          <t>4/5/2026 12:17</t>
         </is>
       </c>
       <c r="I150" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>4/5/2026 13:16</t>
+          <t>4/5/2026 12:25</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>4/5/2026 14:02</t>
+          <t>4/5/2026 13:11</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="M150" t="n">
-        <v>148</v>
+        <v>97</v>
       </c>
       <c r="N150" t="n">
-        <v>59</v>
+        <v>8</v>
       </c>
     </row>
     <row r="151">
@@ -11252,48 +11252,48 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>4/5/2026 08:05</t>
+          <t>4/5/2026 08:07</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>4/5/2026 08:14</t>
+          <t>4/5/2026 08:16</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>4/5/2026 08:14</t>
+          <t>4/5/2026 08:23</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>4/5/2026 08:16</t>
+          <t>4/5/2026 08:25</t>
         </is>
       </c>
       <c r="I159" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>4/5/2026 08:16</t>
+          <t>4/5/2026 08:25</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>4/5/2026 08:36</t>
+          <t>4/5/2026 08:45</t>
         </is>
       </c>
       <c r="L159" t="n">
         <v>0</v>
       </c>
       <c r="M159" t="n">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="160">
@@ -11338,22 +11338,22 @@
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>4/5/2026 08:36</t>
+          <t>4/5/2026 08:45</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>4/5/2026 09:03</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
       <c r="L160" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M160" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="N160" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="161">
@@ -11625,35 +11625,35 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:16</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>4/5/2026 09:15</t>
+          <t>4/5/2026 09:18</t>
         </is>
       </c>
       <c r="I165" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>4/5/2026 09:15</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>4/5/2026 09:23</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M165" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="N165" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="166">
@@ -11805,16 +11805,16 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>4/5/2026 11:50</t>
+          <t>4/5/2026 11:52</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>4/5/2026 11:53</t>
+          <t>4/5/2026 11:55</t>
         </is>
       </c>
       <c r="I168" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M168" t="n">
         <v>48</v>
@@ -11878,22 +11878,22 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>4/5/2026 09:04</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>4/5/2026 09:07</t>
+          <t>4/5/2026 09:16</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M169" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="N169" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="170">
@@ -11938,22 +11938,22 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>4/5/2026 11:49</t>
+          <t>4/5/2026 11:59</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>4/5/2026 12:12</t>
+          <t>4/5/2026 12:22</t>
         </is>
       </c>
       <c r="L170" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M170" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="N170" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="171">
@@ -12418,22 +12418,22 @@
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>4/5/2026 08:39</t>
+          <t>4/5/2026 08:48</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:18</t>
         </is>
       </c>
       <c r="L178" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M178" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="N178" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="179">
@@ -12572,25 +12572,25 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>4/5/2026 12:41</t>
+          <t>4/5/2026 12:23</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>4/5/2026 12:53</t>
+          <t>4/5/2026 12:35</t>
         </is>
       </c>
       <c r="F181" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>4/5/2026 12:53</t>
+          <t>4/5/2026 12:35</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>4/5/2026 12:55</t>
+          <t>4/5/2026 12:37</t>
         </is>
       </c>
       <c r="I181" t="n">
@@ -12598,22 +12598,22 @@
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>4/5/2026 13:15</t>
+          <t>4/5/2026 12:37</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>4/5/2026 13:46</t>
+          <t>4/5/2026 13:08</t>
         </is>
       </c>
       <c r="L181" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M181" t="n">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="N181" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182">
@@ -13138,22 +13138,22 @@
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:05</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:08</t>
         </is>
       </c>
       <c r="L190" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M190" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="N190" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="191">
@@ -13832,48 +13832,48 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>4/5/2026 11:13</t>
+          <t>4/5/2026 11:16</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>4/5/2026 11:23</t>
+          <t>4/5/2026 11:26</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>4/5/2026 11:23</t>
+          <t>4/5/2026 11:28</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>4/5/2026 11:25</t>
+          <t>4/5/2026 11:30</t>
         </is>
       </c>
       <c r="I202" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>4/5/2026 11:25</t>
+          <t>4/5/2026 11:30</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>4/5/2026 11:45</t>
+          <t>4/5/2026 11:50</t>
         </is>
       </c>
       <c r="L202" t="n">
         <v>0</v>
       </c>
       <c r="M202" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="N202" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="203">
@@ -13892,25 +13892,25 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>4/5/2026 11:23</t>
+          <t>4/5/2026 11:03</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>4/5/2026 11:36</t>
+          <t>4/5/2026 11:16</t>
         </is>
       </c>
       <c r="F203" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>4/5/2026 11:36</t>
+          <t>4/5/2026 11:16</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>4/5/2026 11:38</t>
+          <t>4/5/2026 11:18</t>
         </is>
       </c>
       <c r="I203" t="n">
@@ -13918,22 +13918,22 @@
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>4/5/2026 11:57</t>
+          <t>4/5/2026 11:18</t>
         </is>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>4/5/2026 12:34</t>
+          <t>4/5/2026 11:55</t>
         </is>
       </c>
       <c r="L203" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M203" t="n">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="N203" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
     </row>
     <row r="204">
@@ -14325,35 +14325,35 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>4/5/2026 12:46</t>
+          <t>4/5/2026 12:50</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>4/5/2026 12:49</t>
+          <t>4/5/2026 12:53</t>
         </is>
       </c>
       <c r="I210" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>4/5/2026 12:49</t>
+          <t>4/5/2026 12:54</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>4/5/2026 13:19</t>
+          <t>4/5/2026 13:24</t>
         </is>
       </c>
       <c r="L210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M210" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="N210" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="211">

--- a/Thesis_TSSP_NEW_M1_Results_10_Scenarios.xlsx
+++ b/Thesis_TSSP_NEW_M1_Results_10_Scenarios.xlsx
@@ -468,7 +468,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4/5/2026 15:48</t>
+          <t>4/5/2026 15:35</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -478,7 +478,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>4/5/2026 15:48</t>
+          <t>4/5/2026 07:46</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -488,7 +488,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4/5/2026 15:48</t>
+          <t>4/5/2026 10:56</t>
         </is>
       </c>
     </row>
@@ -500,32 +500,32 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4/5/2026 15:48</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4/5/2026 15:48</t>
+          <t>4/5/2026 15:35</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4/5/2026 15:48</t>
+          <t>4/5/2026 12:16</t>
         </is>
       </c>
     </row>
@@ -542,17 +542,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4/5/2026 15:48</t>
+          <t>4/5/2026 11:50</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4/5/2026 15:48</t>
+          <t>4/5/2026 09:27</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -562,7 +562,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>4/5/2026 15:48</t>
+          <t>4/5/2026 13:02</t>
         </is>
       </c>
     </row>
@@ -574,32 +574,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 08:53</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4/5/2026 15:48</t>
+          <t>4/5/2026 15:35</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4/5/2026 15:48</t>
+          <t>4/5/2026 10:25</t>
         </is>
       </c>
     </row>
@@ -611,32 +611,32 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4/5/2026 15:48</t>
+          <t>4/5/2026 09:08</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>4/5/2026 09:08</t>
+          <t>4/5/2026 15:33</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4/5/2026 12:42</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
     </row>
@@ -648,22 +648,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:19</t>
+          <t>4/5/2026 07:20</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:20</t>
+          <t>4/5/2026 15:33</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -673,7 +673,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>4/5/2026 07:20</t>
+          <t>4/5/2026 07:32</t>
         </is>
       </c>
     </row>
@@ -685,12 +685,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4/5/2026 06:48</t>
+          <t>4/5/2026 07:30</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -700,7 +700,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4/5/2026 07:03</t>
+          <t>4/5/2026 06:49</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -710,7 +710,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4/5/2026 06:48</t>
+          <t>4/5/2026 07:04</t>
         </is>
       </c>
     </row>
@@ -722,32 +722,32 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4/5/2026 09:23</t>
+          <t>4/5/2026 15:31</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>4/5/2026 09:25</t>
+          <t>4/5/2026 12:39</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 10:38</t>
         </is>
       </c>
     </row>
@@ -759,32 +759,32 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 15:15</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4/5/2026 08:27</t>
+          <t>4/5/2026 15:31</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4/5/2026 10:16</t>
+          <t>4/5/2026 11:24</t>
         </is>
       </c>
     </row>
@@ -796,32 +796,32 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Unload Gate 4</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4/5/2026 07:27</t>
+          <t>4/5/2026 13:37</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4/5/2026 07:38</t>
+          <t>4/5/2026 08:24</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4/5/2026 07:27</t>
+          <t>4/5/2026 08:40</t>
         </is>
       </c>
     </row>
@@ -833,32 +833,32 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4/5/2026 10:46</t>
+          <t>4/5/2026 12:15</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4/5/2026 09:29</t>
+          <t>4/5/2026 15:32</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4/5/2026 08:09</t>
+          <t>4/5/2026 11:50</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4/5/2026 08:25</t>
+          <t>4/5/2026 12:52</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4/5/2026 08:24</t>
+          <t>4/5/2026 08:39</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4/5/2026 12:17</t>
+          <t>4/5/2026 11:53</t>
         </is>
       </c>
     </row>
@@ -907,12 +907,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4/5/2026 13:02</t>
+          <t>4/5/2026 13:19</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -922,17 +922,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4/5/2026 08:40</t>
+          <t>4/5/2026 14:53</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4/5/2026 13:42</t>
+          <t>4/5/2026 09:15</t>
         </is>
       </c>
     </row>
@@ -944,22 +944,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4/5/2026 15:47</t>
+          <t>4/5/2026 06:18</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4/5/2026 06:18</t>
+          <t>4/5/2026 10:06</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>4/5/2026 08:12</t>
+          <t>4/5/2026 06:21</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4/5/2026 07:08</t>
+          <t>4/5/2026 12:01</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Transport Cart 2</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4/5/2026 07:14</t>
+          <t>4/5/2026 11:19</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4/5/2026 12:19</t>
+          <t>4/5/2026 07:51</t>
         </is>
       </c>
     </row>
@@ -1018,32 +1018,32 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4/5/2026 10:44</t>
+          <t>4/5/2026 11:31</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:11</t>
+          <t>4/5/2026 10:29</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Infeed Station 3</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4/5/2026 12:00</t>
+          <t>4/5/2026 09:42</t>
         </is>
       </c>
     </row>
@@ -1055,22 +1055,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Unload Gate 3</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4/5/2026 15:45</t>
+          <t>4/5/2026 11:10</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Transport Cart 3</t>
+          <t>Transport Cart 1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4/5/2026 15:21</t>
+          <t>4/5/2026 14:44</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4/5/2026 12:53</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
     </row>
@@ -1092,22 +1092,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Unload Gate 2</t>
+          <t>Unload Gate 1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4/5/2026 15:35</t>
+          <t>4/5/2026 13:36</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>4/5/2026 13:03</t>
+          <t>4/5/2026 10:58</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>4/5/2026 10:58</t>
+          <t>4/5/2026 10:05</t>
         </is>
       </c>
     </row>
@@ -1134,27 +1134,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4/5/2026 08:25</t>
+          <t>4/5/2026 15:27</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4/5/2026 11:17</t>
+          <t>4/5/2026 13:10</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Infeed Station 2</t>
+          <t>Infeed Station 3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4/5/2026 09:02</t>
+          <t>4/5/2026 10:27</t>
         </is>
       </c>
     </row>
@@ -1166,12 +1166,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4/5/2026 13:45</t>
+          <t>4/5/2026 12:56</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4/5/2026 14:33</t>
+          <t>4/5/2026 08:33</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4/5/2026 15:48</t>
+          <t>4/5/2026 12:07</t>
         </is>
       </c>
     </row>
@@ -1203,32 +1203,32 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Unload Gate 1</t>
+          <t>Unload Gate 4</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4/5/2026 13:32</t>
+          <t>4/5/2026 09:06</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Transport Cart 1</t>
+          <t>Transport Cart 2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4/5/2026 10:39</t>
+          <t>4/5/2026 08:56</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Infeed Station 1</t>
+          <t>Infeed Station 2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>4/5/2026 15:46</t>
+          <t>4/5/2026 09:07</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>435.90 min</t>
+          <t>433.90 min</t>
         </is>
       </c>
     </row>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.98 min</t>
+          <t>40.97 min</t>
         </is>
       </c>
     </row>
@@ -1300,7 +1300,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>88.60 min</t>
+          <t>91.60 min</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>99.00 min</t>
+          <t>119.00 min</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>16.30 min</t>
+          <t>27.00 min</t>
         </is>
       </c>
     </row>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.00/5.40/9.80 min</t>
+          <t>10.00/7.00/10.00 min</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1057323 / 63646</t>
+          <t>1027503 / 62766</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>38.3130 sec</t>
+          <t>63.9200 sec</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0.5614 %</t>
+          <t>1.4965 %</t>
         </is>
       </c>
     </row>
@@ -1437,7 +1437,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21">
@@ -1457,7 +1457,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>30.67 min | 96.00 min</t>
+          <t>41.52 min | 88.00 min</t>
         </is>
       </c>
     </row>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>32.43 min | 95.00 min</t>
+          <t>39.95 min | 88.00 min</t>
         </is>
       </c>
     </row>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>33.52 min | 99.00 min</t>
+          <t>47.62 min | 92.00 min</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>29.90 min | 80.00 min</t>
+          <t>42.14 min | 88.00 min</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1550,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>32.81 min | 78.00 min</t>
+          <t>41.62 min | 88.00 min</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>32.14 min | 84.00 min</t>
+          <t>39.14 min | 88.00 min</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>34.29 min | 85.00 min</t>
+          <t>37.71 min | 88.00 min</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>33.19 min | 97.00 min</t>
+          <t>42.71 min | 89.00 min</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>30.57 min | 92.00 min</t>
+          <t>38.43 min | 119.00 min</t>
         </is>
       </c>
     </row>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>30.24 min | 80.00 min</t>
+          <t>38.81 min | 88.00 min</t>
         </is>
       </c>
     </row>
@@ -1637,7 +1637,7 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>11.63</v>
+        <v>16.36</v>
       </c>
     </row>
     <row r="41">
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>11.63</v>
+        <v>16.36</v>
       </c>
     </row>
     <row r="42">
@@ -1657,7 +1657,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>18.61</v>
+        <v>9.35</v>
       </c>
     </row>
     <row r="43">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>6.98</v>
+        <v>7.01</v>
       </c>
     </row>
     <row r="44">
@@ -1677,7 +1677,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4.1</v>
+        <v>5.49</v>
       </c>
     </row>
     <row r="45">
@@ -1687,7 +1687,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>3.64</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="46">
@@ -1697,7 +1697,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.82</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="47">
@@ -1707,7 +1707,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>29.36</v>
+        <v>21.07</v>
       </c>
     </row>
     <row r="48">
@@ -1717,7 +1717,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>25.17</v>
+        <v>37.93</v>
       </c>
     </row>
     <row r="49">
@@ -1727,7 +1727,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>33.56</v>
+        <v>29.5</v>
       </c>
     </row>
   </sheetData>
@@ -1892,25 +1892,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4/5/2026 11:34</t>
+          <t>4/5/2026 11:36</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4/5/2026 12:10</t>
+          <t>4/5/2026 12:12</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4/5/2026 12:10</t>
+          <t>4/5/2026 12:12</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4/5/2026 12:12</t>
+          <t>4/5/2026 12:14</t>
         </is>
       </c>
       <c r="I3" t="n">
@@ -1918,22 +1918,22 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4/5/2026 12:24</t>
+          <t>4/5/2026 12:16</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>4/5/2026 13:10</t>
+          <t>4/5/2026 13:02</t>
         </is>
       </c>
       <c r="L3" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="N3" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
@@ -2012,48 +2012,48 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4/5/2026 09:53</t>
+          <t>4/5/2026 10:03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4/5/2026 09:56</t>
+          <t>4/5/2026 10:06</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>4/5/2026 09:56</t>
+          <t>4/5/2026 10:13</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4/5/2026 09:58</t>
+          <t>4/5/2026 10:15</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4/5/2026 09:58</t>
+          <t>4/5/2026 10:25</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>4/5/2026 10:05</t>
+          <t>4/5/2026 10:32</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M5" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
@@ -2192,25 +2192,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4/5/2026 06:48</t>
+          <t>4/5/2026 06:53</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>4/5/2026 06:57</t>
+          <t>4/5/2026 07:02</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4/5/2026 06:57</t>
+          <t>4/5/2026 07:02</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4/5/2026 06:59</t>
+          <t>4/5/2026 07:04</t>
         </is>
       </c>
       <c r="I8" t="n">
@@ -2218,22 +2218,22 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4/5/2026 06:59</t>
+          <t>4/5/2026 07:04</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>4/5/2026 07:22</t>
+          <t>4/5/2026 07:27</t>
         </is>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -2278,22 +2278,22 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4/5/2026 10:37</t>
+          <t>4/5/2026 10:38</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>4/5/2026 11:06</t>
+          <t>4/5/2026 11:07</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -2312,48 +2312,48 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4/5/2026 10:42</t>
+          <t>4/5/2026 10:52</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4/5/2026 10:55</t>
+          <t>4/5/2026 11:05</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4/5/2026 10:55</t>
+          <t>4/5/2026 11:12</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4/5/2026 10:57</t>
+          <t>4/5/2026 11:14</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4/5/2026 10:57</t>
+          <t>4/5/2026 11:24</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4/5/2026 11:09</t>
+          <t>4/5/2026 11:36</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M10" t="n">
+        <v>54</v>
+      </c>
+      <c r="N10" t="n">
         <v>27</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -2432,48 +2432,48 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4/5/2026 08:05</t>
+          <t>4/5/2026 08:15</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4/5/2026 08:13</t>
+          <t>4/5/2026 08:23</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>4/5/2026 08:13</t>
+          <t>4/5/2026 08:30</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>4/5/2026 08:14</t>
+          <t>4/5/2026 08:31</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4/5/2026 08:14</t>
+          <t>4/5/2026 08:41</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>4/5/2026 08:34</t>
+          <t>4/5/2026 09:01</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M12" t="n">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13">
@@ -2492,48 +2492,48 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:13</t>
+          <t>4/5/2026 11:20</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:25</t>
+          <t>4/5/2026 11:32</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:25</t>
+          <t>4/5/2026 11:39</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:28</t>
+          <t>4/5/2026 11:42</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:33</t>
+          <t>4/5/2026 11:48</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>4/5/2026 11:53</t>
+          <t>4/5/2026 12:08</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M13" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -2552,48 +2552,48 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4/5/2026 08:40</t>
+          <t>4/5/2026 08:50</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4/5/2026 08:46</t>
+          <t>4/5/2026 08:56</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>4/5/2026 08:46</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>4/5/2026 08:47</t>
+          <t>4/5/2026 09:04</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>4/5/2026 08:47</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>4/5/2026 09:15</t>
+          <t>4/5/2026 09:42</t>
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M14" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2638,22 +2638,22 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>4/5/2026 06:20</t>
+          <t>4/5/2026 06:21</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>4/5/2026 06:22</t>
+          <t>4/5/2026 06:23</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -2672,48 +2672,48 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4/5/2026 07:08</t>
+          <t>4/5/2026 07:18</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4/5/2026 07:18</t>
+          <t>4/5/2026 07:28</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>4/5/2026 07:18</t>
+          <t>4/5/2026 07:35</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4/5/2026 07:20</t>
+          <t>4/5/2026 07:37</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>4/5/2026 07:20</t>
+          <t>4/5/2026 07:47</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>4/5/2026 07:27</t>
+          <t>4/5/2026 07:54</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M16" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17">
@@ -2732,48 +2732,48 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:29</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:36</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:38</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:42</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>4/5/2026 09:30</t>
+          <t>4/5/2026 09:51</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M17" t="n">
+        <v>42</v>
+      </c>
+      <c r="N17" t="n">
         <v>21</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2792,48 +2792,48 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:04</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:29</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:14</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:14</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 09:39</t>
         </is>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -2912,48 +2912,48 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4/5/2026 08:45</t>
+          <t>4/5/2026 08:55</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>4/5/2026 08:59</t>
+          <t>4/5/2026 09:09</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>4/5/2026 08:59</t>
+          <t>4/5/2026 09:16</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>4/5/2026 09:00</t>
+          <t>4/5/2026 09:17</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>4/5/2026 09:00</t>
+          <t>4/5/2026 09:27</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>4/5/2026 09:26</t>
+          <t>4/5/2026 09:53</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M20" t="n">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21">
@@ -2985,35 +2985,35 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4/5/2026 11:51</t>
+          <t>4/5/2026 11:57</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4/5/2026 11:54</t>
+          <t>4/5/2026 12:00</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>4/5/2026 11:54</t>
+          <t>4/5/2026 12:07</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>4/5/2026 12:24</t>
+          <t>4/5/2026 12:37</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M21" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="22">
@@ -3032,25 +3032,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4/5/2026 08:56</t>
+          <t>4/5/2026 08:57</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4/5/2026 09:04</t>
+          <t>4/5/2026 09:05</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>4/5/2026 09:04</t>
+          <t>4/5/2026 09:05</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4/5/2026 09:06</t>
+          <t>4/5/2026 09:07</t>
         </is>
       </c>
       <c r="I22" t="n">
@@ -3058,22 +3058,22 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>4/5/2026 09:06</t>
+          <t>4/5/2026 09:07</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -3092,48 +3092,48 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4/5/2026 11:43</t>
+          <t>4/5/2026 11:38</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4/5/2026 11:53</t>
+          <t>4/5/2026 11:48</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>4/5/2026 11:54</t>
+          <t>4/5/2026 11:48</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>4/5/2026 11:56</t>
+          <t>4/5/2026 11:50</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>4/5/2026 11:56</t>
+          <t>4/5/2026 11:50</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>4/5/2026 12:19</t>
+          <t>4/5/2026 12:13</t>
         </is>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="N23" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -3178,22 +3178,22 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>4/5/2026 12:23</t>
+          <t>4/5/2026 12:16</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>4/5/2026 13:09</t>
+          <t>4/5/2026 13:02</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M24" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="N24" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -3225,35 +3225,35 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>4/5/2026 12:58</t>
+          <t>4/5/2026 13:00</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>4/5/2026 13:00</t>
+          <t>4/5/2026 13:02</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>4/5/2026 13:00</t>
+          <t>4/5/2026 13:02</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>4/5/2026 13:07</t>
+          <t>4/5/2026 13:09</t>
         </is>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -3272,48 +3272,48 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>4/5/2026 09:53</t>
+          <t>4/5/2026 10:03</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>4/5/2026 09:55</t>
+          <t>4/5/2026 10:05</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>4/5/2026 09:55</t>
+          <t>4/5/2026 10:12</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>4/5/2026 09:57</t>
+          <t>4/5/2026 10:14</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>4/5/2026 09:57</t>
+          <t>4/5/2026 10:24</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>4/5/2026 10:04</t>
+          <t>4/5/2026 10:31</t>
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M26" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27">
@@ -3358,22 +3358,22 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>4/5/2026 09:11</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M27" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -3452,25 +3452,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4/5/2026 06:48</t>
+          <t>4/5/2026 06:51</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>4/5/2026 06:59</t>
+          <t>4/5/2026 07:02</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>4/5/2026 06:59</t>
+          <t>4/5/2026 07:02</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4/5/2026 07:01</t>
+          <t>4/5/2026 07:04</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -3478,22 +3478,22 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>4/5/2026 07:01</t>
+          <t>4/5/2026 07:04</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>4/5/2026 07:24</t>
+          <t>4/5/2026 07:27</t>
         </is>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -3512,48 +3512,48 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4/5/2026 10:26</t>
+          <t>4/5/2026 10:36</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>4/5/2026 10:34</t>
+          <t>4/5/2026 10:44</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>4/5/2026 10:34</t>
+          <t>4/5/2026 10:50</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>4/5/2026 10:36</t>
+          <t>4/5/2026 10:52</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>4/5/2026 10:36</t>
+          <t>4/5/2026 10:52</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>4/5/2026 11:05</t>
+          <t>4/5/2026 11:21</t>
         </is>
       </c>
       <c r="L30" t="n">
         <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>39</v>
+        <v>55</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="31">
@@ -3585,35 +3585,35 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>4/5/2026 12:56</t>
+          <t>4/5/2026 12:47</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4/5/2026 12:58</t>
+          <t>4/5/2026 12:49</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>4/5/2026 13:13</t>
+          <t>4/5/2026 12:49</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>4/5/2026 13:42</t>
+          <t>4/5/2026 13:18</t>
         </is>
       </c>
       <c r="L31" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>61</v>
+        <v>37</v>
       </c>
       <c r="N31" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -3692,48 +3692,48 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4/5/2026 11:41</t>
+          <t>4/5/2026 11:47</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>4/5/2026 11:49</t>
+          <t>4/5/2026 11:55</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>4/5/2026 11:49</t>
+          <t>4/5/2026 11:57</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>4/5/2026 11:50</t>
+          <t>4/5/2026 11:58</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>4/5/2026 11:50</t>
+          <t>4/5/2026 11:58</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>4/5/2026 11:56</t>
+          <t>4/5/2026 12:04</t>
         </is>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34">
@@ -3752,48 +3752,48 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>4/5/2026 08:24</t>
+          <t>4/5/2026 08:34</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>4/5/2026 08:37</t>
+          <t>4/5/2026 08:47</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>4/5/2026 08:37</t>
+          <t>4/5/2026 08:54</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>4/5/2026 08:38</t>
+          <t>4/5/2026 08:55</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>4/5/2026 08:38</t>
+          <t>4/5/2026 09:05</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>4/5/2026 09:05</t>
+          <t>4/5/2026 09:32</t>
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M34" t="n">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35">
@@ -3898,22 +3898,22 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>4/5/2026 06:19</t>
+          <t>4/5/2026 06:21</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>4/5/2026 06:21</t>
+          <t>4/5/2026 06:23</t>
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M36" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
@@ -3932,48 +3932,48 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>4/5/2026 07:08</t>
+          <t>4/5/2026 07:18</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>4/5/2026 07:19</t>
+          <t>4/5/2026 07:29</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>4/5/2026 07:19</t>
+          <t>4/5/2026 07:36</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4/5/2026 07:21</t>
+          <t>4/5/2026 07:38</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>4/5/2026 07:21</t>
+          <t>4/5/2026 07:48</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>4/5/2026 07:28</t>
+          <t>4/5/2026 07:55</t>
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M37" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38">
@@ -3992,48 +3992,48 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:37</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 09:39</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 09:42</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>4/5/2026 09:31</t>
+          <t>4/5/2026 09:51</t>
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M38" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39">
@@ -4052,48 +4052,48 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>4/5/2026 09:04</t>
+          <t>4/5/2026 09:06</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>4/5/2026 09:11</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>4/5/2026 09:11</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:32</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:40</t>
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M39" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40">
@@ -4112,48 +4112,48 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>4/5/2026 09:16</t>
+          <t>4/5/2026 09:26</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>4/5/2026 09:33</t>
+          <t>4/5/2026 09:43</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>4/5/2026 09:33</t>
+          <t>4/5/2026 09:50</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>4/5/2026 09:35</t>
+          <t>4/5/2026 09:52</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>4/5/2026 09:35</t>
+          <t>4/5/2026 10:02</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>4/5/2026 09:55</t>
+          <t>4/5/2026 10:22</t>
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M40" t="n">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41">
@@ -4198,22 +4198,22 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>4/5/2026 10:23</t>
+          <t>4/5/2026 10:27</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>4/5/2026 10:50</t>
+          <t>4/5/2026 10:54</t>
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M41" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
@@ -4232,48 +4232,48 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4/5/2026 11:28</t>
+          <t>4/5/2026 11:38</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>4/5/2026 11:37</t>
+          <t>4/5/2026 11:47</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>4/5/2026 11:45</t>
+          <t>4/5/2026 11:54</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>4/5/2026 11:48</t>
+          <t>4/5/2026 11:57</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>4/5/2026 11:58</t>
+          <t>4/5/2026 12:07</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>4/5/2026 12:23</t>
+          <t>4/5/2026 12:32</t>
         </is>
       </c>
       <c r="L42" t="n">
         <v>10</v>
       </c>
       <c r="M42" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="N42" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="43">
@@ -4292,25 +4292,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4/5/2026 08:57</t>
+          <t>4/5/2026 08:56</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>4/5/2026 09:03</t>
+          <t>4/5/2026 09:02</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>4/5/2026 09:03</t>
+          <t>4/5/2026 09:02</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>4/5/2026 09:05</t>
+          <t>4/5/2026 09:04</t>
         </is>
       </c>
       <c r="I43" t="n">
@@ -4318,22 +4318,22 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>4/5/2026 09:05</t>
+          <t>4/5/2026 09:07</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>4/5/2026 09:08</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M43" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N43" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -4352,48 +4352,48 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>4/5/2026 07:46</t>
+          <t>4/5/2026 07:56</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>4/5/2026 07:57</t>
+          <t>4/5/2026 08:07</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>4/5/2026 07:57</t>
+          <t>4/5/2026 08:14</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>4/5/2026 07:59</t>
+          <t>4/5/2026 08:16</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>4/5/2026 07:59</t>
+          <t>4/5/2026 08:26</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>4/5/2026 08:26</t>
+          <t>4/5/2026 08:53</t>
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M44" t="n">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45">
@@ -4498,22 +4498,22 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>4/5/2026 13:00</t>
+          <t>4/5/2026 13:02</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>4/5/2026 13:07</t>
+          <t>4/5/2026 13:09</t>
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M46" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -4532,48 +4532,48 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4/5/2026 08:53</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>4/5/2026 08:55</t>
+          <t>4/5/2026 09:05</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>4/5/2026 08:55</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>4/5/2026 08:56</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>4/5/2026 08:56</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>4/5/2026 09:02</t>
+          <t>4/5/2026 09:29</t>
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M47" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="48">
@@ -4618,22 +4618,22 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>4/5/2026 09:11</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M48" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49">
@@ -4652,25 +4652,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>4/5/2026 07:19</t>
+          <t>4/5/2026 07:20</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>4/5/2026 07:29</t>
+          <t>4/5/2026 07:30</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>4/5/2026 07:29</t>
+          <t>4/5/2026 07:30</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>4/5/2026 07:31</t>
+          <t>4/5/2026 07:32</t>
         </is>
       </c>
       <c r="I49" t="n">
@@ -4678,22 +4678,22 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>4/5/2026 07:31</t>
+          <t>4/5/2026 07:32</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>4/5/2026 07:47</t>
+          <t>4/5/2026 07:48</t>
         </is>
       </c>
       <c r="L49" t="n">
         <v>0</v>
       </c>
       <c r="M49" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -4738,22 +4738,22 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>4/5/2026 07:02</t>
+          <t>4/5/2026 07:04</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>4/5/2026 07:25</t>
+          <t>4/5/2026 07:27</t>
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M50" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -4772,48 +4772,48 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>4/5/2026 09:33</t>
+          <t>4/5/2026 09:43</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>4/5/2026 09:33</t>
+          <t>4/5/2026 09:50</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:51</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 10:01</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>4/5/2026 10:15</t>
+          <t>4/5/2026 10:42</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M51" t="n">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="52">
@@ -4832,48 +4832,48 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>4/5/2026 10:42</t>
+          <t>4/5/2026 10:52</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>4/5/2026 11:00</t>
+          <t>4/5/2026 11:10</t>
         </is>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>4/5/2026 11:00</t>
+          <t>4/5/2026 11:17</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>4/5/2026 11:02</t>
+          <t>4/5/2026 11:19</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>4/5/2026 11:02</t>
+          <t>4/5/2026 11:24</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>4/5/2026 11:14</t>
+          <t>4/5/2026 11:36</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M52" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53">
@@ -4892,48 +4892,48 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>4/5/2026 07:25</t>
+          <t>4/5/2026 07:35</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>4/5/2026 07:31</t>
+          <t>4/5/2026 07:41</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>4/5/2026 07:31</t>
+          <t>4/5/2026 07:48</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>4/5/2026 07:34</t>
+          <t>4/5/2026 07:51</t>
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>4/5/2026 07:34</t>
+          <t>4/5/2026 08:01</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>4/5/2026 07:49</t>
+          <t>4/5/2026 08:16</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M53" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="54">
@@ -4952,25 +4952,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>4/5/2026 08:10</t>
+          <t>4/5/2026 08:15</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>4/5/2026 08:17</t>
+          <t>4/5/2026 08:22</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>4/5/2026 08:24</t>
+          <t>4/5/2026 08:29</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>4/5/2026 08:26</t>
+          <t>4/5/2026 08:31</t>
         </is>
       </c>
       <c r="I54" t="n">
@@ -4978,22 +4978,22 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>4/5/2026 08:26</t>
+          <t>4/5/2026 08:41</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>4/5/2026 08:46</t>
+          <t>4/5/2026 09:01</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M54" t="n">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="N54" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="55">
@@ -5012,48 +5012,48 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>4/5/2026 11:13</t>
+          <t>4/5/2026 11:23</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>4/5/2026 11:24</t>
+          <t>4/5/2026 11:34</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>4/5/2026 11:24</t>
+          <t>4/5/2026 11:41</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>4/5/2026 11:26</t>
+          <t>4/5/2026 11:43</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>4/5/2026 11:26</t>
+          <t>4/5/2026 11:53</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>4/5/2026 11:46</t>
+          <t>4/5/2026 12:13</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M55" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="56">
@@ -5072,48 +5072,48 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>4/5/2026 08:40</t>
+          <t>4/5/2026 08:50</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>4/5/2026 08:45</t>
+          <t>4/5/2026 08:55</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>4/5/2026 08:45</t>
+          <t>4/5/2026 09:02</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>4/5/2026 08:47</t>
+          <t>4/5/2026 09:04</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>4/5/2026 08:47</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>4/5/2026 09:15</t>
+          <t>4/5/2026 09:42</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M56" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57">
@@ -5158,22 +5158,22 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>4/5/2026 06:20</t>
+          <t>4/5/2026 06:21</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>4/5/2026 06:22</t>
+          <t>4/5/2026 06:23</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M57" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -5192,48 +5192,48 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>4/5/2026 07:08</t>
+          <t>4/5/2026 07:18</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>4/5/2026 07:20</t>
+          <t>4/5/2026 07:30</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>4/5/2026 07:20</t>
+          <t>4/5/2026 07:37</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>4/5/2026 07:21</t>
+          <t>4/5/2026 07:38</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>4/5/2026 07:21</t>
+          <t>4/5/2026 07:48</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>4/5/2026 07:28</t>
+          <t>4/5/2026 07:55</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M58" t="n">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="N58" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="59">
@@ -5252,48 +5252,48 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>4/5/2026 09:18</t>
+          <t>4/5/2026 09:28</t>
         </is>
       </c>
       <c r="F59" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>4/5/2026 09:18</t>
+          <t>4/5/2026 09:32</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:34</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:42</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>4/5/2026 09:29</t>
+          <t>4/5/2026 09:51</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M59" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="N59" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="60">
@@ -5312,48 +5312,48 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>4/5/2026 09:04</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:29</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>4/5/2026 09:14</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>4/5/2026 09:14</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 09:39</t>
         </is>
       </c>
       <c r="L60" t="n">
         <v>0</v>
       </c>
       <c r="M60" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="61">
@@ -5445,35 +5445,35 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>4/5/2026 08:52</t>
+          <t>4/5/2026 08:50</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>4/5/2026 08:55</t>
+          <t>4/5/2026 08:53</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>4/5/2026 09:10</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>4/5/2026 09:59</t>
+          <t>4/5/2026 09:52</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="M62" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="N62" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="63">
@@ -5492,48 +5492,48 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>4/5/2026 10:01</t>
+          <t>4/5/2026 10:11</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>4/5/2026 10:12</t>
+          <t>4/5/2026 10:22</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>4/5/2026 10:13</t>
+          <t>4/5/2026 10:29</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>4/5/2026 10:15</t>
+          <t>4/5/2026 10:31</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>4/5/2026 10:15</t>
+          <t>4/5/2026 10:41</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>4/5/2026 10:39</t>
+          <t>4/5/2026 11:05</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M63" t="n">
-        <v>38</v>
+        <v>64</v>
       </c>
       <c r="N63" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
     </row>
     <row r="64">
@@ -5565,35 +5565,35 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>4/5/2026 09:02</t>
+          <t>4/5/2026 09:04</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>4/5/2026 09:03</t>
+          <t>4/5/2026 09:05</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>4/5/2026 09:03</t>
+          <t>4/5/2026 09:07</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>4/5/2026 09:06</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M64" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="N64" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
@@ -5612,48 +5612,48 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>4/5/2026 07:46</t>
+          <t>4/5/2026 07:56</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>4/5/2026 07:55</t>
+          <t>4/5/2026 08:05</t>
         </is>
       </c>
       <c r="F65" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>4/5/2026 07:55</t>
+          <t>4/5/2026 08:12</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>4/5/2026 07:57</t>
+          <t>4/5/2026 08:14</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>4/5/2026 07:57</t>
+          <t>4/5/2026 08:24</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>4/5/2026 08:24</t>
+          <t>4/5/2026 08:51</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M65" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="N65" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="66">
@@ -5685,35 +5685,35 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>4/5/2026 12:06</t>
+          <t>4/5/2026 12:07</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>4/5/2026 12:08</t>
+          <t>4/5/2026 12:09</t>
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>4/5/2026 12:08</t>
+          <t>4/5/2026 12:16</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>4/5/2026 12:54</t>
+          <t>4/5/2026 13:02</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M66" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67">
@@ -5732,48 +5732,48 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>4/5/2026 06:00</t>
+          <t>4/5/2026 06:10</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>4/5/2026 06:01</t>
+          <t>4/5/2026 06:11</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>4/5/2026 06:01</t>
+          <t>4/5/2026 06:18</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>4/5/2026 06:03</t>
+          <t>4/5/2026 06:20</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>4/5/2026 06:03</t>
+          <t>4/5/2026 06:30</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>4/5/2026 06:05</t>
+          <t>4/5/2026 06:32</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M67" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="N67" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="68">
@@ -5792,48 +5792,48 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4/5/2026 08:53</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>4/5/2026 08:55</t>
+          <t>4/5/2026 09:05</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>4/5/2026 08:55</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>4/5/2026 08:57</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>4/5/2026 08:57</t>
+          <t>4/5/2026 09:24</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>4/5/2026 09:03</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M68" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="N68" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="69">
@@ -5878,22 +5878,22 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M69" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N69" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -5912,25 +5912,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>4/5/2026 07:19</t>
+          <t>4/5/2026 07:20</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>4/5/2026 07:29</t>
+          <t>4/5/2026 07:30</t>
         </is>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>4/5/2026 07:29</t>
+          <t>4/5/2026 07:30</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>4/5/2026 07:31</t>
+          <t>4/5/2026 07:32</t>
         </is>
       </c>
       <c r="I70" t="n">
@@ -5938,22 +5938,22 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>4/5/2026 07:31</t>
+          <t>4/5/2026 07:32</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>4/5/2026 07:47</t>
+          <t>4/5/2026 07:48</t>
         </is>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -5998,22 +5998,22 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>4/5/2026 07:03</t>
+          <t>4/5/2026 07:04</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>4/5/2026 07:26</t>
+          <t>4/5/2026 07:27</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M71" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -6032,48 +6032,48 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>4/5/2026 09:29</t>
+          <t>4/5/2026 09:39</t>
         </is>
       </c>
       <c r="F72" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>4/5/2026 09:29</t>
+          <t>4/5/2026 09:46</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>4/5/2026 09:30</t>
+          <t>4/5/2026 09:47</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>4/5/2026 09:33</t>
+          <t>4/5/2026 09:57</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>4/5/2026 10:14</t>
+          <t>4/5/2026 10:38</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M72" t="n">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="N72" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
     </row>
     <row r="73">
@@ -6332,48 +6332,48 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>4/5/2026 08:40</t>
+          <t>4/5/2026 08:50</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>4/5/2026 08:47</t>
+          <t>4/5/2026 08:57</t>
         </is>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>4/5/2026 08:47</t>
+          <t>4/5/2026 09:04</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>4/5/2026 08:48</t>
+          <t>4/5/2026 09:05</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>4/5/2026 08:48</t>
+          <t>4/5/2026 09:15</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>4/5/2026 09:16</t>
+          <t>4/5/2026 09:43</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M77" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="78">
@@ -6512,48 +6512,48 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 09:26</t>
         </is>
       </c>
       <c r="F80" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 09:32</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>4/5/2026 09:24</t>
+          <t>4/5/2026 09:34</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>4/5/2026 09:24</t>
+          <t>4/5/2026 09:43</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>4/5/2026 09:33</t>
+          <t>4/5/2026 09:52</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M80" t="n">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="N80" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="81">
@@ -6572,48 +6572,48 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>4/5/2026 09:04</t>
+          <t>4/5/2026 09:06</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>4/5/2026 09:11</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>4/5/2026 09:11</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:22</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:39</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M81" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="82">
@@ -6632,48 +6632,48 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>4/5/2026 09:16</t>
+          <t>4/5/2026 09:26</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:44</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:51</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>4/5/2026 09:36</t>
+          <t>4/5/2026 09:53</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>4/5/2026 09:36</t>
+          <t>4/5/2026 10:03</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>4/5/2026 09:56</t>
+          <t>4/5/2026 10:23</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M82" t="n">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="83">
@@ -6692,48 +6692,48 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>4/5/2026 08:45</t>
+          <t>4/5/2026 08:55</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>4/5/2026 08:56</t>
+          <t>4/5/2026 09:06</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>4/5/2026 08:56</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>4/5/2026 08:57</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>4/5/2026 09:03</t>
+          <t>4/5/2026 09:24</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>4/5/2026 09:29</t>
+          <t>4/5/2026 09:50</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M83" t="n">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="N83" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
     </row>
     <row r="84">
@@ -6752,48 +6752,48 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>4/5/2026 10:01</t>
+          <t>4/5/2026 10:11</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>4/5/2026 10:13</t>
+          <t>4/5/2026 10:23</t>
         </is>
       </c>
       <c r="F84" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>4/5/2026 10:13</t>
+          <t>4/5/2026 10:30</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>4/5/2026 10:15</t>
+          <t>4/5/2026 10:32</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>4/5/2026 10:15</t>
+          <t>4/5/2026 10:42</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>4/5/2026 10:39</t>
+          <t>4/5/2026 11:06</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M84" t="n">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="85">
@@ -6825,35 +6825,35 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>4/5/2026 09:03</t>
+          <t>4/5/2026 09:05</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>4/5/2026 09:05</t>
+          <t>4/5/2026 09:07</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>4/5/2026 09:05</t>
+          <t>4/5/2026 09:07</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>4/5/2026 09:08</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="L85" t="n">
         <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N85" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="86">
@@ -6945,35 +6945,35 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>4/5/2026 12:04</t>
+          <t>4/5/2026 12:07</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>4/5/2026 12:06</t>
+          <t>4/5/2026 12:09</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>4/5/2026 12:06</t>
+          <t>4/5/2026 12:16</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>4/5/2026 12:52</t>
+          <t>4/5/2026 13:02</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M87" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="88">
@@ -7052,29 +7052,29 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>4/5/2026 12:50</t>
+          <t>4/5/2026 12:55</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>4/5/2026 12:55</t>
+          <t>4/5/2026 13:00</t>
         </is>
       </c>
       <c r="F89" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>4/5/2026 12:55</t>
+          <t>4/5/2026 13:07</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>4/5/2026 12:57</t>
+          <t>4/5/2026 13:09</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
@@ -7087,7 +7087,7 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
         <v>46</v>
@@ -7138,22 +7138,22 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M90" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="91">
@@ -7198,22 +7198,22 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>4/5/2026 07:29</t>
+          <t>4/5/2026 07:32</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>4/5/2026 07:45</t>
+          <t>4/5/2026 07:48</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M91" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="92">
@@ -7232,25 +7232,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>4/5/2026 06:48</t>
+          <t>4/5/2026 06:49</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>4/5/2026 07:00</t>
+          <t>4/5/2026 07:01</t>
         </is>
       </c>
       <c r="F92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>4/5/2026 07:00</t>
+          <t>4/5/2026 07:01</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>4/5/2026 07:03</t>
+          <t>4/5/2026 07:04</t>
         </is>
       </c>
       <c r="I92" t="n">
@@ -7258,22 +7258,22 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>4/5/2026 07:03</t>
+          <t>4/5/2026 07:04</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>4/5/2026 07:26</t>
+          <t>4/5/2026 07:27</t>
         </is>
       </c>
       <c r="L92" t="n">
         <v>0</v>
       </c>
       <c r="M92" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="93">
@@ -7292,48 +7292,48 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>4/5/2026 09:29</t>
+          <t>4/5/2026 09:39</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>4/5/2026 09:29</t>
+          <t>4/5/2026 09:46</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>4/5/2026 09:30</t>
+          <t>4/5/2026 09:47</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:57</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>4/5/2026 10:15</t>
+          <t>4/5/2026 10:38</t>
         </is>
       </c>
       <c r="L93" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="M93" t="n">
-        <v>55</v>
+        <v>78</v>
       </c>
       <c r="N93" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
     </row>
     <row r="94">
@@ -7352,48 +7352,48 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>4/5/2026 08:27</t>
+          <t>4/5/2026 08:35</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>4/5/2026 08:37</t>
+          <t>4/5/2026 08:45</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>4/5/2026 08:37</t>
+          <t>4/5/2026 08:52</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>4/5/2026 08:39</t>
+          <t>4/5/2026 08:54</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>4/5/2026 08:39</t>
+          <t>4/5/2026 08:57</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:27</t>
         </is>
       </c>
       <c r="L94" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M94" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="95">
@@ -7412,48 +7412,48 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>4/5/2026 07:25</t>
+          <t>4/5/2026 07:35</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>4/5/2026 07:30</t>
+          <t>4/5/2026 07:40</t>
         </is>
       </c>
       <c r="F95" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>4/5/2026 07:30</t>
+          <t>4/5/2026 07:47</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>4/5/2026 07:32</t>
+          <t>4/5/2026 07:49</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>4/5/2026 07:32</t>
+          <t>4/5/2026 07:59</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>4/5/2026 07:47</t>
+          <t>4/5/2026 08:14</t>
         </is>
       </c>
       <c r="L95" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M95" t="n">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="N95" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="96">
@@ -7592,48 +7592,48 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>4/5/2026 08:40</t>
+          <t>4/5/2026 08:50</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>4/5/2026 08:45</t>
+          <t>4/5/2026 08:55</t>
         </is>
       </c>
       <c r="F98" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>4/5/2026 08:45</t>
+          <t>4/5/2026 09:02</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>4/5/2026 08:47</t>
+          <t>4/5/2026 09:04</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>4/5/2026 08:47</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>4/5/2026 09:15</t>
+          <t>4/5/2026 09:42</t>
         </is>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M98" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="99">
@@ -7665,35 +7665,35 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>4/5/2026 06:18</t>
+          <t>4/5/2026 06:19</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>4/5/2026 06:20</t>
+          <t>4/5/2026 06:21</t>
         </is>
       </c>
       <c r="I99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>4/5/2026 06:20</t>
+          <t>4/5/2026 06:21</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>4/5/2026 06:22</t>
+          <t>4/5/2026 06:23</t>
         </is>
       </c>
       <c r="L99" t="n">
         <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="100">
@@ -7738,22 +7738,22 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>4/5/2026 07:50</t>
+          <t>4/5/2026 07:51</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>4/5/2026 07:54</t>
+          <t>4/5/2026 07:55</t>
         </is>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M100" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="N100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="101">
@@ -7772,48 +7772,48 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:15</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>4/5/2026 09:23</t>
+          <t>4/5/2026 09:29</t>
         </is>
       </c>
       <c r="F101" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>4/5/2026 09:23</t>
+          <t>4/5/2026 09:36</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>4/5/2026 09:25</t>
+          <t>4/5/2026 09:38</t>
         </is>
       </c>
       <c r="I101" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>4/5/2026 09:25</t>
+          <t>4/5/2026 09:42</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:51</t>
         </is>
       </c>
       <c r="L101" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M101" t="n">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="N101" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="102">
@@ -7832,48 +7832,48 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>4/5/2026 09:04</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>4/5/2026 09:11</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="F102" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>4/5/2026 09:11</t>
+          <t>4/5/2026 09:28</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="I102" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:39</t>
         </is>
       </c>
       <c r="L102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M102" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="N102" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="103">
@@ -7892,48 +7892,48 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>4/5/2026 09:16</t>
+          <t>4/5/2026 09:26</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:44</t>
         </is>
       </c>
       <c r="F103" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:51</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:54</t>
         </is>
       </c>
       <c r="I103" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 10:04</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>4/5/2026 09:57</t>
+          <t>4/5/2026 10:24</t>
         </is>
       </c>
       <c r="L103" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M103" t="n">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="N103" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="104">
@@ -7952,48 +7952,48 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>4/5/2026 08:45</t>
+          <t>4/5/2026 08:55</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>4/5/2026 08:58</t>
+          <t>4/5/2026 09:08</t>
         </is>
       </c>
       <c r="F104" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>4/5/2026 08:58</t>
+          <t>4/5/2026 09:15</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>4/5/2026 09:00</t>
+          <t>4/5/2026 09:17</t>
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:27</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>4/5/2026 09:35</t>
+          <t>4/5/2026 09:53</t>
         </is>
       </c>
       <c r="L104" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M104" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="N104" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="105">
@@ -8025,35 +8025,35 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>4/5/2026 12:50</t>
+          <t>4/5/2026 12:43</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>4/5/2026 12:52</t>
+          <t>4/5/2026 12:45</t>
         </is>
       </c>
       <c r="I105" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>4/5/2026 12:52</t>
+          <t>4/5/2026 12:45</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>4/5/2026 13:22</t>
+          <t>4/5/2026 13:15</t>
         </is>
       </c>
       <c r="L105" t="n">
         <v>0</v>
       </c>
       <c r="M105" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="N105" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -8132,25 +8132,25 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>4/5/2026 10:39</t>
+          <t>4/5/2026 10:42</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>4/5/2026 10:47</t>
+          <t>4/5/2026 10:50</t>
         </is>
       </c>
       <c r="F107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>4/5/2026 10:47</t>
+          <t>4/5/2026 10:50</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>4/5/2026 10:49</t>
+          <t>4/5/2026 10:52</t>
         </is>
       </c>
       <c r="I107" t="n">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>4/5/2026 10:49</t>
+          <t>4/5/2026 10:56</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>4/5/2026 11:19</t>
+          <t>4/5/2026 11:26</t>
         </is>
       </c>
       <c r="L107" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M107" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="108">
@@ -8205,35 +8205,35 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>4/5/2026 12:10</t>
+          <t>4/5/2026 12:14</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>4/5/2026 12:12</t>
+          <t>4/5/2026 12:16</t>
         </is>
       </c>
       <c r="I108" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>4/5/2026 12:12</t>
+          <t>4/5/2026 12:16</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>4/5/2026 12:58</t>
+          <t>4/5/2026 13:02</t>
         </is>
       </c>
       <c r="L108" t="n">
         <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="N108" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="109">
@@ -8252,48 +8252,48 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>4/5/2026 06:00</t>
+          <t>4/5/2026 06:10</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>4/5/2026 06:02</t>
+          <t>4/5/2026 06:12</t>
         </is>
       </c>
       <c r="F109" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>4/5/2026 06:02</t>
+          <t>4/5/2026 06:19</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>4/5/2026 06:03</t>
+          <t>4/5/2026 06:20</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>4/5/2026 06:03</t>
+          <t>4/5/2026 06:30</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>4/5/2026 06:05</t>
+          <t>4/5/2026 06:32</t>
         </is>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M109" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="N109" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="110">
@@ -8385,35 +8385,35 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:11</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>4/5/2026 09:11</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="I111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>4/5/2026 09:11</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="L111" t="n">
         <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -8445,35 +8445,35 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>4/5/2026 07:28</t>
+          <t>4/5/2026 07:30</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>4/5/2026 07:30</t>
+          <t>4/5/2026 07:32</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>4/5/2026 07:30</t>
+          <t>4/5/2026 07:32</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>4/5/2026 07:46</t>
+          <t>4/5/2026 07:48</t>
         </is>
       </c>
       <c r="L112" t="n">
         <v>0</v>
       </c>
       <c r="M112" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="N112" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="113">
@@ -8492,25 +8492,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>4/5/2026 06:48</t>
+          <t>4/5/2026 06:50</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>4/5/2026 06:58</t>
+          <t>4/5/2026 07:00</t>
         </is>
       </c>
       <c r="F113" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>4/5/2026 06:58</t>
+          <t>4/5/2026 07:00</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>4/5/2026 07:00</t>
+          <t>4/5/2026 07:02</t>
         </is>
       </c>
       <c r="I113" t="n">
@@ -8518,22 +8518,22 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>4/5/2026 07:00</t>
+          <t>4/5/2026 07:04</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>4/5/2026 07:23</t>
+          <t>4/5/2026 07:27</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M113" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="114">
@@ -8625,35 +8625,35 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>4/5/2026 08:37</t>
+          <t>4/5/2026 08:43</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>4/5/2026 08:40</t>
+          <t>4/5/2026 08:46</t>
         </is>
       </c>
       <c r="I115" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>4/5/2026 08:40</t>
+          <t>4/5/2026 08:46</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>4/5/2026 09:10</t>
+          <t>4/5/2026 09:16</t>
         </is>
       </c>
       <c r="L115" t="n">
         <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="116">
@@ -8732,48 +8732,48 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>4/5/2026 08:05</t>
+          <t>4/5/2026 08:15</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>4/5/2026 08:14</t>
+          <t>4/5/2026 08:24</t>
         </is>
       </c>
       <c r="F117" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>4/5/2026 08:14</t>
+          <t>4/5/2026 08:31</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>4/5/2026 08:15</t>
+          <t>4/5/2026 08:32</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>4/5/2026 08:15</t>
+          <t>4/5/2026 08:42</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>4/5/2026 08:35</t>
+          <t>4/5/2026 09:02</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M117" t="n">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="N117" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="118">
@@ -8938,22 +8938,22 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>4/5/2026 06:20</t>
+          <t>4/5/2026 06:21</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>4/5/2026 06:22</t>
+          <t>4/5/2026 06:23</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M120" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N120" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -9032,48 +9032,48 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>4/5/2026 09:18</t>
+          <t>4/5/2026 09:28</t>
         </is>
       </c>
       <c r="F122" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>4/5/2026 09:18</t>
+          <t>4/5/2026 09:35</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:37</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J122" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 09:42</t>
         </is>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>4/5/2026 09:31</t>
+          <t>4/5/2026 09:51</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="M122" t="n">
+        <v>42</v>
+      </c>
+      <c r="N122" t="n">
         <v>22</v>
-      </c>
-      <c r="N122" t="n">
-        <v>2</v>
       </c>
     </row>
     <row r="123">
@@ -9092,48 +9092,48 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>4/5/2026 09:04</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>4/5/2026 09:10</t>
+          <t>4/5/2026 09:20</t>
         </is>
       </c>
       <c r="F123" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>4/5/2026 09:10</t>
+          <t>4/5/2026 09:27</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:29</t>
         </is>
       </c>
       <c r="I123" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:39</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M123" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="N123" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="124">
@@ -9152,42 +9152,42 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>4/5/2026 12:41</t>
+          <t>4/5/2026 12:36</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>4/5/2026 12:58</t>
+          <t>4/5/2026 12:53</t>
         </is>
       </c>
       <c r="F124" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>4/5/2026 13:06</t>
+          <t>4/5/2026 13:00</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
+          <t>4/5/2026 13:02</t>
+        </is>
+      </c>
+      <c r="I124" t="n">
+        <v>7</v>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
           <t>4/5/2026 13:08</t>
         </is>
       </c>
-      <c r="I124" t="n">
-        <v>8</v>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>4/5/2026 13:08</t>
-        </is>
-      </c>
       <c r="K124" t="inlineStr">
         <is>
           <t>4/5/2026 13:37</t>
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M124" t="n">
         <v>71</v>
@@ -9272,48 +9272,48 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>4/5/2026 08:32</t>
+          <t>4/5/2026 08:42</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>4/5/2026 08:47</t>
+          <t>4/5/2026 08:57</t>
         </is>
       </c>
       <c r="F126" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>4/5/2026 08:47</t>
+          <t>4/5/2026 09:04</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>4/5/2026 08:49</t>
+          <t>4/5/2026 09:06</t>
         </is>
       </c>
       <c r="I126" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J126" t="inlineStr">
         <is>
-          <t>4/5/2026 08:49</t>
+          <t>4/5/2026 09:16</t>
         </is>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 09:49</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M126" t="n">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="N126" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="127">
@@ -9345,35 +9345,35 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>4/5/2026 09:04</t>
+          <t>4/5/2026 09:05</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>4/5/2026 09:06</t>
+          <t>4/5/2026 09:07</t>
         </is>
       </c>
       <c r="I127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>4/5/2026 09:06</t>
+          <t>4/5/2026 09:07</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="L127" t="n">
         <v>0</v>
       </c>
       <c r="M127" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N127" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="128">
@@ -9392,48 +9392,48 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>4/5/2026 07:46</t>
+          <t>4/5/2026 07:56</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>4/5/2026 07:56</t>
+          <t>4/5/2026 08:06</t>
         </is>
       </c>
       <c r="F128" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>4/5/2026 07:56</t>
+          <t>4/5/2026 08:13</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>4/5/2026 07:58</t>
+          <t>4/5/2026 08:15</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>4/5/2026 07:58</t>
+          <t>4/5/2026 08:25</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>4/5/2026 08:25</t>
+          <t>4/5/2026 08:52</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M128" t="n">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="129">
@@ -9452,48 +9452,48 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>4/5/2026 11:34</t>
+          <t>4/5/2026 11:35</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>4/5/2026 12:11</t>
+          <t>4/5/2026 12:12</t>
         </is>
       </c>
       <c r="F129" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>4/5/2026 12:11</t>
+          <t>4/5/2026 12:14</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>4/5/2026 12:13</t>
+          <t>4/5/2026 12:16</t>
         </is>
       </c>
       <c r="I129" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>4/5/2026 12:13</t>
+          <t>4/5/2026 12:16</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>4/5/2026 12:59</t>
+          <t>4/5/2026 13:02</t>
         </is>
       </c>
       <c r="L129" t="n">
         <v>0</v>
       </c>
       <c r="M129" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="N129" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="130">
@@ -9538,22 +9538,22 @@
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>4/5/2026 12:59</t>
+          <t>4/5/2026 13:02</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>4/5/2026 13:06</t>
+          <t>4/5/2026 13:09</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M130" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="131">
@@ -9658,22 +9658,22 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>4/5/2026 09:11</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M132" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="N132" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
@@ -9718,22 +9718,22 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>4/5/2026 07:31</t>
+          <t>4/5/2026 07:32</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>4/5/2026 07:47</t>
+          <t>4/5/2026 07:48</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M133" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N133" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="134">
@@ -9752,25 +9752,25 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>4/5/2026 06:48</t>
+          <t>4/5/2026 06:52</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>4/5/2026 06:57</t>
+          <t>4/5/2026 07:01</t>
         </is>
       </c>
       <c r="F134" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>4/5/2026 06:57</t>
+          <t>4/5/2026 07:01</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>4/5/2026 07:00</t>
+          <t>4/5/2026 07:04</t>
         </is>
       </c>
       <c r="I134" t="n">
@@ -9778,22 +9778,22 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>4/5/2026 07:00</t>
+          <t>4/5/2026 07:04</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>4/5/2026 07:23</t>
+          <t>4/5/2026 07:27</t>
         </is>
       </c>
       <c r="L134" t="n">
         <v>0</v>
       </c>
       <c r="M134" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N134" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="135">
@@ -9872,48 +9872,48 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>4/5/2026 12:41</t>
+          <t>4/5/2026 12:51</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>4/5/2026 12:46</t>
+          <t>4/5/2026 12:56</t>
         </is>
       </c>
       <c r="F136" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>4/5/2026 12:55</t>
+          <t>4/5/2026 13:03</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>4/5/2026 12:57</t>
+          <t>4/5/2026 13:05</t>
         </is>
       </c>
       <c r="I136" t="n">
+        <v>7</v>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>4/5/2026 13:14</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>4/5/2026 13:43</t>
+        </is>
+      </c>
+      <c r="L136" t="n">
         <v>9</v>
       </c>
-      <c r="J136" t="inlineStr">
-        <is>
-          <t>4/5/2026 13:12</t>
-        </is>
-      </c>
-      <c r="K136" t="inlineStr">
-        <is>
-          <t>4/5/2026 13:41</t>
-        </is>
-      </c>
-      <c r="L136" t="n">
-        <v>15</v>
-      </c>
       <c r="M136" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="N136" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="137">
@@ -10018,22 +10018,22 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>4/5/2026 11:52</t>
+          <t>4/5/2026 11:54</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>4/5/2026 11:58</t>
+          <t>4/5/2026 12:00</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M138" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N138" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139">
@@ -10292,48 +10292,48 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>4/5/2026 09:18</t>
+          <t>4/5/2026 09:28</t>
         </is>
       </c>
       <c r="F143" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>4/5/2026 09:18</t>
+          <t>4/5/2026 09:35</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:36</t>
         </is>
       </c>
       <c r="I143" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:42</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>4/5/2026 09:28</t>
+          <t>4/5/2026 09:51</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M143" t="n">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
     </row>
     <row r="144">
@@ -10352,48 +10352,48 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>4/5/2026 09:04</t>
+          <t>4/5/2026 09:05</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>4/5/2026 09:11</t>
+          <t>4/5/2026 09:12</t>
         </is>
       </c>
       <c r="F144" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>4/5/2026 09:11</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="I144" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:39</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M144" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="N144" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="145">
@@ -10412,29 +10412,29 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>4/5/2026 12:31</t>
+          <t>4/5/2026 12:36</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>4/5/2026 12:48</t>
+          <t>4/5/2026 12:53</t>
         </is>
       </c>
       <c r="F145" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>4/5/2026 12:58</t>
+          <t>4/5/2026 13:00</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>4/5/2026 13:00</t>
+          <t>4/5/2026 13:02</t>
         </is>
       </c>
       <c r="I145" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J145" t="inlineStr">
         <is>
@@ -10447,7 +10447,7 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M145" t="n">
         <v>75</v>
@@ -10558,22 +10558,22 @@
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>4/5/2026 12:59</t>
+          <t>4/5/2026 12:44</t>
         </is>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>4/5/2026 13:29</t>
+          <t>4/5/2026 13:14</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M147" t="n">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="N147" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148">
@@ -10618,22 +10618,22 @@
       </c>
       <c r="J148" t="inlineStr">
         <is>
-          <t>4/5/2026 09:05</t>
+          <t>4/5/2026 09:07</t>
         </is>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>4/5/2026 09:08</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M148" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N148" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
@@ -10652,48 +10652,48 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>4/5/2026 07:46</t>
+          <t>4/5/2026 07:56</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>4/5/2026 07:56</t>
+          <t>4/5/2026 08:06</t>
         </is>
       </c>
       <c r="F149" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>4/5/2026 07:56</t>
+          <t>4/5/2026 08:13</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>4/5/2026 07:58</t>
+          <t>4/5/2026 08:15</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J149" t="inlineStr">
         <is>
-          <t>4/5/2026 07:58</t>
+          <t>4/5/2026 08:25</t>
         </is>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>4/5/2026 08:25</t>
+          <t>4/5/2026 08:52</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M149" t="n">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="150">
@@ -10738,22 +10738,22 @@
       </c>
       <c r="J150" t="inlineStr">
         <is>
-          <t>4/5/2026 12:25</t>
+          <t>4/5/2026 12:17</t>
         </is>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>4/5/2026 13:11</t>
+          <t>4/5/2026 13:03</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="M150" t="n">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="N150" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151">
@@ -10772,48 +10772,48 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>4/5/2026 06:00</t>
+          <t>4/5/2026 06:10</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>4/5/2026 06:02</t>
+          <t>4/5/2026 06:12</t>
         </is>
       </c>
       <c r="F151" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>4/5/2026 06:02</t>
+          <t>4/5/2026 06:19</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>4/5/2026 06:04</t>
+          <t>4/5/2026 06:21</t>
         </is>
       </c>
       <c r="I151" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J151" t="inlineStr">
         <is>
-          <t>4/5/2026 06:04</t>
+          <t>4/5/2026 06:31</t>
         </is>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>4/5/2026 06:06</t>
+          <t>4/5/2026 06:33</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M151" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="152">
@@ -10832,48 +10832,48 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>4/5/2026 08:53</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>4/5/2026 08:56</t>
+          <t>4/5/2026 09:06</t>
         </is>
       </c>
       <c r="F152" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>4/5/2026 08:56</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>4/5/2026 08:58</t>
+          <t>4/5/2026 09:15</t>
         </is>
       </c>
       <c r="I152" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>4/5/2026 08:58</t>
+          <t>4/5/2026 09:25</t>
         </is>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>4/5/2026 09:04</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M152" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="N152" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="153">
@@ -10918,22 +10918,22 @@
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="L153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M153" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N153" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="154">
@@ -10978,22 +10978,22 @@
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>4/5/2026 07:31</t>
+          <t>4/5/2026 07:32</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>4/5/2026 07:47</t>
+          <t>4/5/2026 07:48</t>
         </is>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M154" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="155">
@@ -11025,35 +11025,35 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>4/5/2026 07:00</t>
+          <t>4/5/2026 07:01</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>4/5/2026 07:03</t>
+          <t>4/5/2026 07:04</t>
         </is>
       </c>
       <c r="I155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>4/5/2026 07:03</t>
+          <t>4/5/2026 07:04</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t>4/5/2026 07:26</t>
+          <t>4/5/2026 07:27</t>
         </is>
       </c>
       <c r="L155" t="n">
         <v>0</v>
       </c>
       <c r="M155" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N155" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
@@ -11072,25 +11072,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>4/5/2026 10:26</t>
+          <t>4/5/2026 10:32</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>4/5/2026 10:37</t>
+          <t>4/5/2026 10:43</t>
         </is>
       </c>
       <c r="F156" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>4/5/2026 10:37</t>
+          <t>4/5/2026 10:43</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>4/5/2026 10:39</t>
+          <t>4/5/2026 10:45</t>
         </is>
       </c>
       <c r="I156" t="n">
@@ -11098,22 +11098,22 @@
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>4/5/2026 10:39</t>
+          <t>4/5/2026 10:45</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t>4/5/2026 11:08</t>
+          <t>4/5/2026 11:14</t>
         </is>
       </c>
       <c r="L156" t="n">
         <v>0</v>
       </c>
       <c r="M156" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="157">
@@ -11158,22 +11158,22 @@
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>4/5/2026 12:47</t>
+          <t>4/5/2026 12:51</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>4/5/2026 13:16</t>
+          <t>4/5/2026 13:20</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M157" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="158">
@@ -11192,48 +11192,48 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>4/5/2026 07:25</t>
+          <t>4/5/2026 07:35</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>4/5/2026 07:29</t>
+          <t>4/5/2026 07:39</t>
         </is>
       </c>
       <c r="F158" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>4/5/2026 07:29</t>
+          <t>4/5/2026 07:46</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>4/5/2026 07:31</t>
+          <t>4/5/2026 07:48</t>
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J158" t="inlineStr">
         <is>
-          <t>4/5/2026 07:31</t>
+          <t>4/5/2026 07:58</t>
         </is>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>4/5/2026 07:46</t>
+          <t>4/5/2026 08:13</t>
         </is>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M158" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="159">
@@ -11252,25 +11252,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>4/5/2026 08:07</t>
+          <t>4/5/2026 08:15</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>4/5/2026 08:16</t>
+          <t>4/5/2026 08:24</t>
         </is>
       </c>
       <c r="F159" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>4/5/2026 08:23</t>
+          <t>4/5/2026 08:31</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>4/5/2026 08:25</t>
+          <t>4/5/2026 08:33</t>
         </is>
       </c>
       <c r="I159" t="n">
@@ -11278,22 +11278,22 @@
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>4/5/2026 08:25</t>
+          <t>4/5/2026 08:43</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>4/5/2026 08:45</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M159" t="n">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="N159" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="160">
@@ -11312,48 +11312,48 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>4/5/2026 08:24</t>
+          <t>4/5/2026 08:30</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>4/5/2026 08:34</t>
+          <t>4/5/2026 08:40</t>
         </is>
       </c>
       <c r="F160" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>4/5/2026 08:34</t>
+          <t>4/5/2026 08:47</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>4/5/2026 08:35</t>
+          <t>4/5/2026 08:48</t>
         </is>
       </c>
       <c r="I160" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>4/5/2026 08:45</t>
+          <t>4/5/2026 08:58</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:25</t>
         </is>
       </c>
       <c r="L160" t="n">
         <v>10</v>
       </c>
       <c r="M160" t="n">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="N160" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
     </row>
     <row r="161">
@@ -11492,48 +11492,48 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>4/5/2026 07:08</t>
+          <t>4/5/2026 07:18</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>4/5/2026 07:21</t>
+          <t>4/5/2026 07:31</t>
         </is>
       </c>
       <c r="F163" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>4/5/2026 07:21</t>
+          <t>4/5/2026 07:38</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>4/5/2026 07:23</t>
+          <t>4/5/2026 07:40</t>
         </is>
       </c>
       <c r="I163" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>4/5/2026 07:23</t>
+          <t>4/5/2026 07:50</t>
         </is>
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>4/5/2026 07:30</t>
+          <t>4/5/2026 07:57</t>
         </is>
       </c>
       <c r="L163" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M163" t="n">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="N163" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="164">
@@ -11565,35 +11565,35 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:26</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 09:29</t>
         </is>
       </c>
       <c r="I164" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 09:39</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>4/5/2026 09:31</t>
+          <t>4/5/2026 09:48</t>
         </is>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M164" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="165">
@@ -11612,48 +11612,48 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>4/5/2026 09:04</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="F165" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>4/5/2026 09:16</t>
+          <t>4/5/2026 09:29</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>4/5/2026 09:18</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="I165" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>4/5/2026 09:23</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>4/5/2026 09:31</t>
+          <t>4/5/2026 09:39</t>
         </is>
       </c>
       <c r="L165" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M165" t="n">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="N165" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="166">
@@ -11732,48 +11732,48 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>4/5/2026 11:58</t>
+          <t>4/5/2026 12:08</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>4/5/2026 12:07</t>
+          <t>4/5/2026 12:17</t>
         </is>
       </c>
       <c r="F167" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>4/5/2026 12:07</t>
+          <t>4/5/2026 12:18</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>4/5/2026 12:11</t>
+          <t>4/5/2026 12:22</t>
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>4/5/2026 12:11</t>
+          <t>4/5/2026 12:23</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>4/5/2026 12:39</t>
+          <t>4/5/2026 12:51</t>
         </is>
       </c>
       <c r="L167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M167" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="N167" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
     <row r="168">
@@ -11805,35 +11805,35 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>4/5/2026 11:52</t>
+          <t>4/5/2026 11:50</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>4/5/2026 11:55</t>
+          <t>4/5/2026 11:53</t>
         </is>
       </c>
       <c r="I168" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>4/5/2026 11:55</t>
+          <t>4/5/2026 11:53</t>
         </is>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t>4/5/2026 12:25</t>
+          <t>4/5/2026 12:23</t>
         </is>
       </c>
       <c r="L168" t="n">
         <v>0</v>
       </c>
       <c r="M168" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="N168" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169">
@@ -11878,22 +11878,22 @@
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:07</t>
         </is>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t>4/5/2026 09:16</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="L169" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M169" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="N169" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="170">
@@ -11938,22 +11938,22 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>4/5/2026 11:59</t>
+          <t>4/5/2026 11:56</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>4/5/2026 12:22</t>
+          <t>4/5/2026 12:19</t>
         </is>
       </c>
       <c r="L170" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M170" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="N170" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="171">
@@ -11972,48 +11972,48 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>4/5/2026 09:39</t>
+          <t>4/5/2026 09:49</t>
         </is>
       </c>
       <c r="F171" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>4/5/2026 09:39</t>
+          <t>4/5/2026 09:56</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>4/5/2026 09:41</t>
+          <t>4/5/2026 09:58</t>
         </is>
       </c>
       <c r="I171" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>4/5/2026 09:41</t>
+          <t>4/5/2026 10:08</t>
         </is>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>4/5/2026 10:45</t>
+          <t>4/5/2026 11:12</t>
         </is>
       </c>
       <c r="L171" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M171" t="n">
-        <v>92</v>
+        <v>119</v>
       </c>
       <c r="N171" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="172">
@@ -12152,25 +12152,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>4/5/2026 09:08</t>
+          <t>4/5/2026 09:09</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="F174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="I174" t="n">
@@ -12178,22 +12178,22 @@
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="L174" t="n">
         <v>0</v>
       </c>
       <c r="M174" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="175">
@@ -12238,22 +12238,22 @@
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>4/5/2026 07:31</t>
+          <t>4/5/2026 07:32</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t>4/5/2026 07:47</t>
+          <t>4/5/2026 07:48</t>
         </is>
       </c>
       <c r="L175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M175" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="176">
@@ -12392,48 +12392,48 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>4/5/2026 08:27</t>
+          <t>4/5/2026 08:37</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>4/5/2026 08:36</t>
+          <t>4/5/2026 08:46</t>
         </is>
       </c>
       <c r="F178" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>4/5/2026 08:36</t>
+          <t>4/5/2026 08:53</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>4/5/2026 08:39</t>
+          <t>4/5/2026 08:56</t>
         </is>
       </c>
       <c r="I178" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>4/5/2026 08:48</t>
+          <t>4/5/2026 09:06</t>
         </is>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>4/5/2026 09:18</t>
+          <t>4/5/2026 09:36</t>
         </is>
       </c>
       <c r="L178" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M178" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="N178" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="179">
@@ -12452,48 +12452,48 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>4/5/2026 07:25</t>
+          <t>4/5/2026 07:35</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>4/5/2026 07:30</t>
+          <t>4/5/2026 07:40</t>
         </is>
       </c>
       <c r="F179" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>4/5/2026 07:30</t>
+          <t>4/5/2026 07:47</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>4/5/2026 07:32</t>
+          <t>4/5/2026 07:49</t>
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>4/5/2026 07:32</t>
+          <t>4/5/2026 07:59</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>4/5/2026 07:47</t>
+          <t>4/5/2026 08:14</t>
         </is>
       </c>
       <c r="L179" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M179" t="n">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="N179" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="180">
@@ -12632,48 +12632,48 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>4/5/2026 08:40</t>
+          <t>4/5/2026 08:50</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>4/5/2026 08:46</t>
+          <t>4/5/2026 08:56</t>
         </is>
       </c>
       <c r="F182" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>4/5/2026 08:46</t>
+          <t>4/5/2026 09:03</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>4/5/2026 08:47</t>
+          <t>4/5/2026 09:04</t>
         </is>
       </c>
       <c r="I182" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>4/5/2026 08:47</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t>4/5/2026 09:15</t>
+          <t>4/5/2026 09:42</t>
         </is>
       </c>
       <c r="L182" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M182" t="n">
-        <v>35</v>
+        <v>62</v>
       </c>
       <c r="N182" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="183">
@@ -12705,35 +12705,35 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>4/5/2026 06:18</t>
+          <t>4/5/2026 06:19</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>4/5/2026 06:20</t>
+          <t>4/5/2026 06:21</t>
         </is>
       </c>
       <c r="I183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>4/5/2026 06:20</t>
+          <t>4/5/2026 06:21</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t>4/5/2026 06:22</t>
+          <t>4/5/2026 06:23</t>
         </is>
       </c>
       <c r="L183" t="n">
         <v>0</v>
       </c>
       <c r="M183" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N183" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="184">
@@ -12812,48 +12812,48 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:29</t>
         </is>
       </c>
       <c r="F185" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>4/5/2026 09:19</t>
+          <t>4/5/2026 09:36</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:38</t>
         </is>
       </c>
       <c r="I185" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:42</t>
         </is>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t>4/5/2026 09:30</t>
+          <t>4/5/2026 09:51</t>
         </is>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M185" t="n">
+        <v>42</v>
+      </c>
+      <c r="N185" t="n">
         <v>21</v>
-      </c>
-      <c r="N185" t="n">
-        <v>0</v>
       </c>
     </row>
     <row r="186">
@@ -12872,48 +12872,48 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>4/5/2026 09:04</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:23</t>
         </is>
       </c>
       <c r="F186" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:28</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>4/5/2026 09:15</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="I186" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>4/5/2026 09:15</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="K186" t="inlineStr">
         <is>
-          <t>4/5/2026 09:23</t>
+          <t>4/5/2026 09:39</t>
         </is>
       </c>
       <c r="L186" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M186" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="N186" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="187">
@@ -12932,48 +12932,48 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>4/5/2026 09:16</t>
+          <t>4/5/2026 09:26</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>4/5/2026 09:35</t>
+          <t>4/5/2026 09:45</t>
         </is>
       </c>
       <c r="F187" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>4/5/2026 09:35</t>
+          <t>4/5/2026 09:52</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 09:54</t>
         </is>
       </c>
       <c r="I187" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>4/5/2026 09:37</t>
+          <t>4/5/2026 10:04</t>
         </is>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t>4/5/2026 09:57</t>
+          <t>4/5/2026 10:24</t>
         </is>
       </c>
       <c r="L187" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M187" t="n">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="N187" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="188">
@@ -13125,35 +13125,35 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>4/5/2026 09:03</t>
+          <t>4/5/2026 09:05</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>4/5/2026 09:05</t>
+          <t>4/5/2026 09:07</t>
         </is>
       </c>
       <c r="I190" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>4/5/2026 09:05</t>
+          <t>4/5/2026 09:07</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t>4/5/2026 09:08</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="L190" t="n">
         <v>0</v>
       </c>
       <c r="M190" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N190" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="191">
@@ -13232,48 +13232,48 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>4/5/2026 11:34</t>
+          <t>4/5/2026 11:35</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>4/5/2026 12:06</t>
+          <t>4/5/2026 12:07</t>
         </is>
       </c>
       <c r="F192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>4/5/2026 12:06</t>
+          <t>4/5/2026 12:14</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>4/5/2026 12:08</t>
+          <t>4/5/2026 12:16</t>
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>4/5/2026 12:08</t>
+          <t>4/5/2026 12:16</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t>4/5/2026 12:54</t>
+          <t>4/5/2026 13:02</t>
         </is>
       </c>
       <c r="L192" t="n">
         <v>0</v>
       </c>
       <c r="M192" t="n">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="N192" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="193">
@@ -13292,48 +13292,48 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>4/5/2026 06:00</t>
+          <t>4/5/2026 06:10</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>4/5/2026 06:01</t>
+          <t>4/5/2026 06:11</t>
         </is>
       </c>
       <c r="F193" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>4/5/2026 06:01</t>
+          <t>4/5/2026 06:18</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>4/5/2026 06:03</t>
+          <t>4/5/2026 06:20</t>
         </is>
       </c>
       <c r="I193" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>4/5/2026 06:03</t>
+          <t>4/5/2026 06:30</t>
         </is>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t>4/5/2026 06:05</t>
+          <t>4/5/2026 06:32</t>
         </is>
       </c>
       <c r="L193" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M193" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="N193" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="194">
@@ -13438,22 +13438,22 @@
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>4/5/2026 09:12</t>
+          <t>4/5/2026 09:13</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="L195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M195" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="196">
@@ -13485,35 +13485,35 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>4/5/2026 07:28</t>
+          <t>4/5/2026 07:30</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>4/5/2026 07:30</t>
+          <t>4/5/2026 07:32</t>
         </is>
       </c>
       <c r="I196" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>4/5/2026 07:30</t>
+          <t>4/5/2026 07:32</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>4/5/2026 07:46</t>
+          <t>4/5/2026 07:48</t>
         </is>
       </c>
       <c r="L196" t="n">
         <v>0</v>
       </c>
       <c r="M196" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="N196" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="197">
@@ -13592,48 +13592,48 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:44</t>
         </is>
       </c>
       <c r="F198" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>4/5/2026 09:34</t>
+          <t>4/5/2026 09:51</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>4/5/2026 09:35</t>
+          <t>4/5/2026 09:52</t>
         </is>
       </c>
       <c r="I198" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>4/5/2026 09:35</t>
+          <t>4/5/2026 10:02</t>
         </is>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t>4/5/2026 10:16</t>
+          <t>4/5/2026 10:43</t>
         </is>
       </c>
       <c r="L198" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M198" t="n">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="N198" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="199">
@@ -13652,48 +13652,48 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>4/5/2026 10:42</t>
+          <t>4/5/2026 10:52</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>4/5/2026 10:56</t>
+          <t>4/5/2026 11:06</t>
         </is>
       </c>
       <c r="F199" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>4/5/2026 10:56</t>
+          <t>4/5/2026 11:13</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>4/5/2026 10:58</t>
+          <t>4/5/2026 11:15</t>
         </is>
       </c>
       <c r="I199" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>4/5/2026 10:58</t>
+          <t>4/5/2026 11:24</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>4/5/2026 11:10</t>
+          <t>4/5/2026 11:36</t>
         </is>
       </c>
       <c r="L199" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="M199" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="N199" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="200">
@@ -13798,22 +13798,22 @@
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>4/5/2026 11:51</t>
+          <t>4/5/2026 11:55</t>
         </is>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t>4/5/2026 11:57</t>
+          <t>4/5/2026 12:01</t>
         </is>
       </c>
       <c r="L201" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M201" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="N201" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="202">
@@ -13832,48 +13832,48 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>4/5/2026 11:16</t>
+          <t>4/5/2026 11:23</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>4/5/2026 11:26</t>
+          <t>4/5/2026 11:33</t>
         </is>
       </c>
       <c r="F202" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>4/5/2026 11:28</t>
+          <t>4/5/2026 11:40</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>4/5/2026 11:30</t>
+          <t>4/5/2026 11:42</t>
         </is>
       </c>
       <c r="I202" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J202" t="inlineStr">
         <is>
-          <t>4/5/2026 11:30</t>
+          <t>4/5/2026 11:52</t>
         </is>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t>4/5/2026 11:50</t>
+          <t>4/5/2026 12:12</t>
         </is>
       </c>
       <c r="L202" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M202" t="n">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="N202" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="203">
@@ -13965,35 +13965,35 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>4/5/2026 06:18</t>
+          <t>4/5/2026 06:19</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>4/5/2026 06:20</t>
+          <t>4/5/2026 06:21</t>
         </is>
       </c>
       <c r="I204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>4/5/2026 06:20</t>
+          <t>4/5/2026 06:21</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>4/5/2026 06:22</t>
+          <t>4/5/2026 06:23</t>
         </is>
       </c>
       <c r="L204" t="n">
         <v>0</v>
       </c>
       <c r="M204" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="N204" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="205">
@@ -14072,48 +14072,48 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>4/5/2026 09:09</t>
+          <t>4/5/2026 09:19</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="F206" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>4/5/2026 09:20</t>
+          <t>4/5/2026 09:34</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 09:36</t>
         </is>
       </c>
       <c r="I206" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>4/5/2026 09:22</t>
+          <t>4/5/2026 09:42</t>
         </is>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t>4/5/2026 09:31</t>
+          <t>4/5/2026 09:51</t>
         </is>
       </c>
       <c r="L206" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M206" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="N206" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="207">
@@ -14132,48 +14132,48 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>4/5/2026 09:04</t>
+          <t>4/5/2026 09:14</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>4/5/2026 09:11</t>
+          <t>4/5/2026 09:21</t>
         </is>
       </c>
       <c r="F207" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>4/5/2026 09:11</t>
+          <t>4/5/2026 09:28</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:30</t>
         </is>
       </c>
       <c r="I207" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>4/5/2026 09:13</t>
+          <t>4/5/2026 09:31</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t>4/5/2026 09:21</t>
+          <t>4/5/2026 09:39</t>
         </is>
       </c>
       <c r="L207" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M207" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="N207" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
     </row>
     <row r="208">
@@ -14192,48 +14192,48 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>4/5/2026 09:16</t>
+          <t>4/5/2026 09:26</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>4/5/2026 09:36</t>
+          <t>4/5/2026 09:46</t>
         </is>
       </c>
       <c r="F208" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>4/5/2026 09:36</t>
+          <t>4/5/2026 09:53</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>4/5/2026 09:38</t>
+          <t>4/5/2026 09:55</t>
         </is>
       </c>
       <c r="I208" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>4/5/2026 09:38</t>
+          <t>4/5/2026 10:05</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>4/5/2026 09:58</t>
+          <t>4/5/2026 10:25</t>
         </is>
       </c>
       <c r="L208" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M208" t="n">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="N208" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
     </row>
     <row r="209">
@@ -14325,35 +14325,35 @@
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>4/5/2026 12:50</t>
+          <t>4/5/2026 12:46</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>4/5/2026 12:53</t>
+          <t>4/5/2026 12:49</t>
         </is>
       </c>
       <c r="I210" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>4/5/2026 12:54</t>
+          <t>4/5/2026 12:49</t>
         </is>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t>4/5/2026 13:24</t>
+          <t>4/5/2026 13:19</t>
         </is>
       </c>
       <c r="L210" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M210" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="N210" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="211">
@@ -14398,22 +14398,22 @@
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>4/5/2026 09:05</t>
+          <t>4/5/2026 09:07</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t>4/5/2026 09:08</t>
+          <t>4/5/2026 09:10</t>
         </is>
       </c>
       <c r="L211" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M211" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="N211" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/Thesis_TSSP_NEW_M1_Results_10_Scenarios.xlsx
+++ b/Thesis_TSSP_NEW_M1_Results_10_Scenarios.xlsx
@@ -1372,7 +1372,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>63.9200 sec</t>
+          <t>61.6020 sec</t>
         </is>
       </c>
     </row>
